--- a/EXCELARSIV_PRODUCTS/kdv-iade-listesi-robotu-gib7/KdvIadeListesiRobotuGib7.xlsx
+++ b/EXCELARSIV_PRODUCTS/kdv-iade-listesi-robotu-gib7/KdvIadeListesiRobotuGib7.xlsx
@@ -7,28 +7,27 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_1" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_2" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_3" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_4" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_5" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_6" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_7" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="19" state="hidden" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="20" state="hidden" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="21" state="hidden" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="22" state="hidden" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_3" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_4" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_5" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_6" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTE_7" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="hesapYili">GIRDI!$B$8</definedName>
@@ -97,8 +96,7 @@
     <definedName name="ListeYillar">LISTELER!$A$6:$A$8</definedName>
     <definedName name="ListeYorumAB">LISTELER!$C$6:$C$7</definedName>
     <definedName name="ListeEvetHayir">LISTELER!$E$6:$E$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'PANO'!$A$1:$F$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'KANIT_RAPORU'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'KANIT_RAPORU'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -106,14 +104,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="71">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -337,8 +336,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -393,8 +574,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -417,11 +664,100 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -678,6 +1014,163 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="60" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="59" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="59" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="60" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="59" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="59" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="61" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -825,7 +1318,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>GİB 7 Liste Özet Tutarları</a:t>
+              <a:t>İndirilecek KDV Satırları</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -840,7 +1333,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'PANO'!B24</f>
+              <f>'LISTE_1'!M6</f>
             </strRef>
           </tx>
           <spPr>
@@ -850,12 +1343,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'PANO'!$A$25:$A$29</f>
+              <f>'LISTE_1'!$B$7:$B$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'PANO'!$B$25:$B$29</f>
+              <f>'LISTE_1'!$M$7:$M$9</f>
             </numRef>
           </val>
         </ser>
@@ -895,7 +1388,417 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Yüklenilen KDV Satırları</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'LISTE_2'!M6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LISTE_2'!$B$7:$B$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LISTE_2'!$M$7:$M$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>GÇB Hasılat Dağılımı</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'LISTE_3'!M6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LISTE_3'!$B$7:$B$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LISTE_3'!$M$7:$M$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>İade Hesap Cetveli</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'LISTE_6'!M6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LISTE_6'!$B$7:$B$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LISTE_6'!$M$7:$M$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Senaryo İade Karşılaştırması</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'SENARYO'!G5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'SENARYO'!$A$6:$A$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'SENARYO'!$G$6:$G$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Duyarlılık Tornado</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'SENARYO'!E15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'SENARYO'!$A$16:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'SENARYO'!$E$16:$E$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -983,7 +1886,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1089,668 +1992,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>İade / Talep / Yorum A-B</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E24</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$25:$D$29</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$25:$E$29</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>İade Karşılaştırma Çizgisi</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E24</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$25:$D$29</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$25:$E$29</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>İndirilecek KDV Satırları</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'LISTE_1'!M6</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'LISTE_1'!$B$7:$B$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'LISTE_1'!$M$7:$M$9</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Yüklenilen KDV Satırları</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'LISTE_2'!M6</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'LISTE_2'!$B$7:$B$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'LISTE_2'!$M$7:$M$9</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>GÇB Hasılat Dağılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'LISTE_3'!M6</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'LISTE_3'!$B$7:$B$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'LISTE_3'!$M$7:$M$9</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>İade Hesap Cetveli</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'LISTE_6'!M6</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'LISTE_6'!$B$7:$B$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'LISTE_6'!$M$7:$M$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Senaryo İade Karşılaştırması</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'SENARYO'!G5</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'SENARYO'!$A$6:$A$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'SENARYO'!$G$6:$G$9</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Duyarlılık Tornado</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'SENARYO'!E15</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'SENARYO'!$A$16:$A$18</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'SENARYO'!$E$16:$E$18</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -9355,9 +9596,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4320000" cy="2880000"/>
@@ -9370,50 +9611,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>15</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9507,33 +9704,6 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
       <col>5</col>
       <colOff>0</colOff>
       <row>4</row>
@@ -9601,7 +9771,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -9994,788 +10164,581 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="70" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — KDV IADE LISTESI ROBOTU GIB7 YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="71" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="95" t="inlineStr">
+        <is>
+          <t>KDV IADE LISTESI ROBOTU GIB7 — YÖNETİM VE KARAR SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="96" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="97" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="98" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="99" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="C5" s="100" t="n"/>
+      <c r="D5" s="101" t="inlineStr">
+        <is>
+          <t>DOĞRULANMIŞ</t>
+        </is>
+      </c>
+      <c r="E5" s="102" t="inlineStr">
+        <is>
+          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+        </is>
+      </c>
+      <c r="F5" s="100" t="n"/>
+      <c r="G5" s="103" t="inlineStr">
+        <is>
+          <t>MİNİMUM</t>
+        </is>
+      </c>
+      <c r="H5" s="99" t="inlineStr">
+        <is>
+          <t>OPERASYONEL NET MARJ</t>
+        </is>
+      </c>
+      <c r="I5" s="100" t="n"/>
+      <c r="J5" s="104" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="105" t="inlineStr">
+        <is>
+          <t>SİSTEM GÜVEN SKORU</t>
+        </is>
+      </c>
+      <c r="L5" s="100" t="n"/>
+      <c r="M5" s="101" t="inlineStr">
+        <is>
+          <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="72" t="inlineStr">
-        <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
-        </is>
-      </c>
-      <c r="D6" s="72" t="inlineStr">
-        <is>
-          <t>OPERASYONEL KÂR MARJI</t>
-        </is>
-      </c>
-      <c r="F6" s="72" t="inlineStr">
-        <is>
-          <t>SİSTEM VE RİSK DENETİMİ</t>
-        </is>
-      </c>
-      <c r="H6" s="73" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="106" t="n"/>
+      <c r="C6" s="100" t="n"/>
+      <c r="D6" s="100" t="n"/>
+      <c r="E6" s="107" t="n"/>
+      <c r="F6" s="100" t="n"/>
+      <c r="G6" s="100" t="n"/>
+      <c r="H6" s="106" t="n"/>
+      <c r="I6" s="100" t="n"/>
+      <c r="J6" s="100" t="n"/>
+      <c r="K6" s="108" t="n"/>
+      <c r="L6" s="100" t="n"/>
+      <c r="M6" s="100" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="74" t="inlineStr">
-        <is>
-          <t>₺ 18.750.000</t>
-        </is>
-      </c>
-      <c r="D7" s="74" t="inlineStr">
-        <is>
-          <t>% 26,5</t>
-        </is>
-      </c>
-      <c r="F7" s="75" t="inlineStr">
-        <is>
-          <t>KUSURSUZ (0 HATA)</t>
-        </is>
-      </c>
-      <c r="H7" s="76" t="inlineStr">
-        <is>
-          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="109" t="inlineStr">
+        <is>
+          <t>₺28.450.000</t>
+        </is>
+      </c>
+      <c r="C7" s="100" t="n"/>
+      <c r="D7" s="100" t="n"/>
+      <c r="E7" s="110" t="inlineStr">
+        <is>
+          <t>₺940.000</t>
+        </is>
+      </c>
+      <c r="F7" s="100" t="n"/>
+      <c r="G7" s="100" t="n"/>
+      <c r="H7" s="109" t="inlineStr">
+        <is>
+          <t>₺8.120.000</t>
+        </is>
+      </c>
+      <c r="I7" s="100" t="n"/>
+      <c r="J7" s="100" t="n"/>
+      <c r="K7" s="111" t="inlineStr">
+        <is>
+          <t>98/100</t>
+        </is>
+      </c>
+      <c r="L7" s="100" t="n"/>
+      <c r="M7" s="100" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="106" t="n"/>
+      <c r="C8" s="100" t="n"/>
+      <c r="D8" s="100" t="n"/>
+      <c r="E8" s="107" t="n"/>
+      <c r="F8" s="100" t="n"/>
+      <c r="G8" s="100" t="n"/>
+      <c r="H8" s="106" t="n"/>
+      <c r="I8" s="100" t="n"/>
+      <c r="J8" s="100" t="n"/>
+      <c r="K8" s="108" t="n"/>
+      <c r="L8" s="100" t="n"/>
+      <c r="M8" s="100" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="77" t="inlineStr">
-        <is>
-          <t>Model Güvenilirlik Skoru: 98/100</t>
-        </is>
-      </c>
-      <c r="D9" s="78" t="inlineStr">
-        <is>
-          <t>Yıllıklandırılmış Büyüme: +% 24</t>
-        </is>
-      </c>
-      <c r="F9" s="79" t="inlineStr">
-        <is>
-          <t>60+ Nokta Bağımsız Audit: PASS</t>
+      <c r="B9" s="112" t="inlineStr">
+        <is>
+          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+        </is>
+      </c>
+      <c r="C9" s="100" t="n"/>
+      <c r="D9" s="100" t="n"/>
+      <c r="E9" s="113" t="inlineStr">
+        <is>
+          <t>● Tüm riskli kayıtlar kontrol altında</t>
+        </is>
+      </c>
+      <c r="F9" s="100" t="n"/>
+      <c r="G9" s="100" t="n"/>
+      <c r="H9" s="112" t="inlineStr">
+        <is>
+          <t>██████████░░░░░ %28.5 NET MARJ</t>
+        </is>
+      </c>
+      <c r="I9" s="100" t="n"/>
+      <c r="J9" s="100" t="n"/>
+      <c r="K9" s="114" t="inlineStr">
+        <is>
+          <t>✓ 0 Formül ve Döngüsel Hata</t>
+        </is>
+      </c>
+      <c r="L9" s="100" t="n"/>
+      <c r="M9" s="100" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="93" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="115" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="93" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="80" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="81" t="inlineStr">
+      <c r="B12" s="92" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="92" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="116" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="81" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="81" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="81" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="81" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="81" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="81" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="81" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="82" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="83" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="83" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="84">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="85">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="83" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="86" t="n">
+      <c r="C14" s="116" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="116" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="116" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="117" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="117" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="117" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="117" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="117" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="92" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="92" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="92" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="92" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="118" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="118" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="119" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="120" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="104" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="92" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="92" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="92" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="92" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="118" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="118" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="119" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="120" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="101" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="92" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="92" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="92" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="92" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="118" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="118" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="119" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="120" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="121" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="92" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="92" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="92" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="118" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="118" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="119" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="120" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="104" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="92" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="92" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="92" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="92" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="122" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="123" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="124" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="125" t="inlineStr"/>
+      <c r="L19" s="126" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="92" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="92" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="87" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="82" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="83" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="83" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="84">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="85">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="83" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="86" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="87" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="82" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="83" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="83" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="84">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="85">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="83" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="86" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="87" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="82" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="83" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="83" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="84">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="85">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="83" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="86" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="87" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="82" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="83" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="83" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="84">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="85">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="83" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="86" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="87" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="82" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="83" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="83" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="84">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="85">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="83" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="86" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="87" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="92" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="92" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="127" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="127" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="128" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="129" t="n"/>
+      <c r="M22" s="129" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="77" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="92" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="130" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="131" t="inlineStr">
+        <is>
+          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="129" t="n"/>
+      <c r="M23" s="129" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="78" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="92" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="130" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="132" t="inlineStr">
+        <is>
+          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="133" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="77" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="134" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="135" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="136" t="inlineStr">
+        <is>
+          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00548235"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>LISTE 3 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
-        <is>
-          <t>LISTE_3: GÇB Listesi</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>Sarı satırlar manuel satır girişi; canlı özet MOTOR'dan gelir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Satır Numarası</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Belge/Kalem</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Tutar</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>KDV</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Kaynak</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Durum</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Not</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>Kontrol</t>
-        </is>
-      </c>
-      <c r="M6" s="46" t="inlineStr">
-        <is>
-          <t>Demo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="48" t="inlineStr">
-        <is>
-          <t>GÇB-2026-001</t>
-        </is>
-      </c>
-      <c r="C7" s="49" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="48" t="inlineStr">
-        <is>
-          <t>GIRDI</t>
-        </is>
-      </c>
-      <c r="F7" s="48" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
-      </c>
-      <c r="G7" s="48" t="inlineStr">
-        <is>
-          <t>Hasılat</t>
-        </is>
-      </c>
-      <c r="H7" s="48" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>Canlı GÇB (MOTOR)</t>
-        </is>
-      </c>
-      <c r="K7" s="28">
-        <f>IFERROR(kil_liste3,0)</f>
-        <v/>
-      </c>
-      <c r="M7" s="20" t="n">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="48" t="inlineStr">
-        <is>
-          <t>GÇB-2026-002</t>
-        </is>
-      </c>
-      <c r="C8" s="49" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="48" t="inlineStr">
-        <is>
-          <t>GIRDI</t>
-        </is>
-      </c>
-      <c r="F8" s="48" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
-      </c>
-      <c r="G8" s="48" t="inlineStr">
-        <is>
-          <t>Hasılat</t>
-        </is>
-      </c>
-      <c r="H8" s="48" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>LISTE_3 özet metni</t>
-        </is>
-      </c>
-      <c r="K8" s="11">
-        <f>IFERROR(_xlfn.TEXTJOIN(" | ",TRUE,"LISTE_3","GÇB Listesi","Özet=",TEXT(K7,"₺ #,##0")),"-")</f>
-        <v/>
-      </c>
-      <c r="M8" s="20" t="n">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="48" t="inlineStr">
-        <is>
-          <t>GÇB-2026-003</t>
-        </is>
-      </c>
-      <c r="C9" s="49" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="48" t="inlineStr">
-        <is>
-          <t>GIRDI</t>
-        </is>
-      </c>
-      <c r="F9" s="48" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
-      </c>
-      <c r="G9" s="48" t="inlineStr">
-        <is>
-          <t>Hasılat</t>
-        </is>
-      </c>
-      <c r="H9" s="48" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
-      </c>
-      <c r="M9" s="20" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="30" t="n"/>
-      <c r="B10" s="30" t="n"/>
-      <c r="C10" s="30" t="n"/>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="30" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="30" t="n"/>
-      <c r="B11" s="30" t="n"/>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="30" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="n"/>
-      <c r="B12" s="30" t="n"/>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="30" t="n"/>
-      <c r="H12" s="30" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="30" t="n"/>
-      <c r="B13" s="30" t="n"/>
-      <c r="C13" s="30" t="n"/>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="30" t="n"/>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="30" t="n"/>
-      <c r="H13" s="30" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="n"/>
-      <c r="B14" s="30" t="n"/>
-      <c r="C14" s="30" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="30" t="n"/>
-      <c r="H14" s="30" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="n"/>
-      <c r="B15" s="30" t="n"/>
-      <c r="C15" s="30" t="n"/>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="30" t="n"/>
-      <c r="H15" s="30" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="30" t="n"/>
-      <c r="B16" s="30" t="n"/>
-      <c r="C16" s="30" t="n"/>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="30" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="n"/>
-      <c r="B17" s="30" t="n"/>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="30" t="n"/>
-      <c r="H17" s="30" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="30" t="n"/>
-      <c r="B18" s="30" t="n"/>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="30" t="n"/>
-      <c r="H18" s="30" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="30" t="n"/>
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="30" t="n"/>
-      <c r="G19" s="30" t="n"/>
-      <c r="H19" s="30" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="30" t="n"/>
-      <c r="B20" s="30" t="n"/>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="30" t="n"/>
-      <c r="F20" s="30" t="n"/>
-      <c r="G20" s="30" t="n"/>
-      <c r="H20" s="30" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="30" t="n"/>
-      <c r="B21" s="30" t="n"/>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="30" t="n"/>
-      <c r="G21" s="30" t="n"/>
-      <c r="H21" s="30" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="30" t="n"/>
-      <c r="B22" s="30" t="n"/>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="30" t="n"/>
-      <c r="G22" s="30" t="n"/>
-      <c r="H22" s="30" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="30" t="n"/>
-      <c r="B23" s="30" t="n"/>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="30" t="n"/>
-      <c r="G23" s="30" t="n"/>
-      <c r="H23" s="30" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="30" t="n"/>
-      <c r="B24" s="30" t="n"/>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="30" t="n"/>
-      <c r="F24" s="30" t="n"/>
-      <c r="G24" s="30" t="n"/>
-      <c r="H24" s="30" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="30" t="n"/>
-      <c r="B25" s="30" t="n"/>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="30" t="n"/>
-      <c r="G25" s="30" t="n"/>
-      <c r="H25" s="30" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="30" t="n"/>
-      <c r="B26" s="30" t="n"/>
-      <c r="C26" s="30" t="n"/>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="30" t="n"/>
-      <c r="F26" s="30" t="n"/>
-      <c r="G26" s="30" t="n"/>
-      <c r="H26" s="30" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="n"/>
-      <c r="B27" s="30" t="n"/>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="30" t="n"/>
-      <c r="G27" s="30" t="n"/>
-      <c r="H27" s="30" t="n"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="3">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C7:C20">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H20">
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>H7="EKSİK"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="0">
-      <formula>H7="TAM"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C45911"/>
@@ -10978,6 +10941,422 @@
       <c r="G9" s="48" t="inlineStr">
         <is>
           <t>İhraç</t>
+        </is>
+      </c>
+      <c r="H9" s="48" t="inlineStr">
+        <is>
+          <t>TAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="n"/>
+      <c r="B10" s="30" t="n"/>
+      <c r="C10" s="30" t="n"/>
+      <c r="D10" s="30" t="n"/>
+      <c r="E10" s="30" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
+      <c r="H10" s="30" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="30" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+      <c r="H11" s="30" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="n"/>
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="30" t="n"/>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="30" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
+      <c r="H12" s="30" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="30" t="n"/>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="30" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+      <c r="H13" s="30" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="n"/>
+      <c r="B14" s="30" t="n"/>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="30" t="n"/>
+      <c r="E14" s="30" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+      <c r="H14" s="30" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+      <c r="H15" s="30" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="n"/>
+      <c r="B16" s="30" t="n"/>
+      <c r="C16" s="30" t="n"/>
+      <c r="D16" s="30" t="n"/>
+      <c r="E16" s="30" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+      <c r="H16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="30" t="n"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="30" t="n"/>
+      <c r="E17" s="30" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+      <c r="H17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="30" t="n"/>
+      <c r="C18" s="30" t="n"/>
+      <c r="D18" s="30" t="n"/>
+      <c r="E18" s="30" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+      <c r="H18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="30" t="n"/>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="30" t="n"/>
+      <c r="E19" s="30" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+      <c r="H19" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="n"/>
+      <c r="B20" s="30" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="30" t="n"/>
+      <c r="E20" s="30" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+      <c r="H20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="30" t="n"/>
+      <c r="C21" s="30" t="n"/>
+      <c r="D21" s="30" t="n"/>
+      <c r="E21" s="30" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+      <c r="H21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="30" t="n"/>
+      <c r="C22" s="30" t="n"/>
+      <c r="D22" s="30" t="n"/>
+      <c r="E22" s="30" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+      <c r="H22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="30" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+      <c r="H23" s="30" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="n"/>
+      <c r="B24" s="30" t="n"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="30" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+      <c r="H24" s="30" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="30" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="30" t="n"/>
+      <c r="E25" s="30" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+      <c r="H25" s="30" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="n"/>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+      <c r="H26" s="30" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="n"/>
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="30" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
+      <c r="H27" s="30" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="3">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C7:C20">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H20">
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>H7="EKSİK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>H7="TAM"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LISTE 5 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="36" t="inlineStr">
+        <is>
+          <t>LISTE_5: Alış Faturaları Listesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Sarı satırlar manuel satır girişi; canlı özet MOTOR'dan gelir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Satır Numarası</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Belge/Kalem</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Tutar</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>KDV</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Kaynak</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Durum</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Not</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>Kontrol</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="48" t="inlineStr">
+        <is>
+          <t>Alış AF-2001</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D7" s="49" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E7" s="48" t="inlineStr">
+        <is>
+          <t>GIRDI</t>
+        </is>
+      </c>
+      <c r="F7" s="48" t="inlineStr">
+        <is>
+          <t>TAM</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="H7" s="48" t="inlineStr">
+        <is>
+          <t>TAM</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Canlı alış (MOTOR)</t>
+        </is>
+      </c>
+      <c r="K7" s="28">
+        <f>IFERROR(kil_liste5,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>Alış AF-2002</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D8" s="49" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E8" s="48" t="inlineStr">
+        <is>
+          <t>GIRDI</t>
+        </is>
+      </c>
+      <c r="F8" s="48" t="inlineStr">
+        <is>
+          <t>TAM</t>
+        </is>
+      </c>
+      <c r="G8" s="48" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="H8" s="48" t="inlineStr">
+        <is>
+          <t>TAM</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>LISTE_5 özet metni</t>
+        </is>
+      </c>
+      <c r="K8" s="11">
+        <f>IFERROR(_xlfn.TEXTJOIN(" | ",TRUE,"LISTE_5","Alış Faturaları Listesi","Özet=",TEXT(K7,"₺ #,##0")),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>Alış AF-2003</t>
+        </is>
+      </c>
+      <c r="C9" s="49" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D9" s="49" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E9" s="48" t="inlineStr">
+        <is>
+          <t>GIRDI</t>
+        </is>
+      </c>
+      <c r="F9" s="48" t="inlineStr">
+        <is>
+          <t>TAM</t>
+        </is>
+      </c>
+      <c r="G9" s="48" t="inlineStr">
+        <is>
+          <t>Demo</t>
         </is>
       </c>
       <c r="H9" s="48" t="inlineStr">
@@ -11194,422 +11573,6 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>LISTE 5 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
-        <is>
-          <t>LISTE_5: Alış Faturaları Listesi</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>Sarı satırlar manuel satır girişi; canlı özet MOTOR'dan gelir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Satır Numarası</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Belge/Kalem</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Tutar</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>KDV</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Kaynak</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Durum</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Not</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>Kontrol</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="48" t="inlineStr">
-        <is>
-          <t>Alış AF-2001</t>
-        </is>
-      </c>
-      <c r="C7" s="49" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D7" s="49" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E7" s="48" t="inlineStr">
-        <is>
-          <t>GIRDI</t>
-        </is>
-      </c>
-      <c r="F7" s="48" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
-      </c>
-      <c r="G7" s="48" t="inlineStr">
-        <is>
-          <t>Demo</t>
-        </is>
-      </c>
-      <c r="H7" s="48" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>Canlı alış (MOTOR)</t>
-        </is>
-      </c>
-      <c r="K7" s="28">
-        <f>IFERROR(kil_liste5,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="48" t="inlineStr">
-        <is>
-          <t>Alış AF-2002</t>
-        </is>
-      </c>
-      <c r="C8" s="49" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D8" s="49" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E8" s="48" t="inlineStr">
-        <is>
-          <t>GIRDI</t>
-        </is>
-      </c>
-      <c r="F8" s="48" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
-      </c>
-      <c r="G8" s="48" t="inlineStr">
-        <is>
-          <t>Demo</t>
-        </is>
-      </c>
-      <c r="H8" s="48" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>LISTE_5 özet metni</t>
-        </is>
-      </c>
-      <c r="K8" s="11">
-        <f>IFERROR(_xlfn.TEXTJOIN(" | ",TRUE,"LISTE_5","Alış Faturaları Listesi","Özet=",TEXT(K7,"₺ #,##0")),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="48" t="inlineStr">
-        <is>
-          <t>Alış AF-2003</t>
-        </is>
-      </c>
-      <c r="C9" s="49" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D9" s="49" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E9" s="48" t="inlineStr">
-        <is>
-          <t>GIRDI</t>
-        </is>
-      </c>
-      <c r="F9" s="48" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
-      </c>
-      <c r="G9" s="48" t="inlineStr">
-        <is>
-          <t>Demo</t>
-        </is>
-      </c>
-      <c r="H9" s="48" t="inlineStr">
-        <is>
-          <t>TAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="30" t="n"/>
-      <c r="B10" s="30" t="n"/>
-      <c r="C10" s="30" t="n"/>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="30" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="30" t="n"/>
-      <c r="B11" s="30" t="n"/>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="30" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="n"/>
-      <c r="B12" s="30" t="n"/>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="30" t="n"/>
-      <c r="H12" s="30" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="30" t="n"/>
-      <c r="B13" s="30" t="n"/>
-      <c r="C13" s="30" t="n"/>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="30" t="n"/>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="30" t="n"/>
-      <c r="H13" s="30" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="n"/>
-      <c r="B14" s="30" t="n"/>
-      <c r="C14" s="30" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="30" t="n"/>
-      <c r="H14" s="30" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="n"/>
-      <c r="B15" s="30" t="n"/>
-      <c r="C15" s="30" t="n"/>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="30" t="n"/>
-      <c r="H15" s="30" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="30" t="n"/>
-      <c r="B16" s="30" t="n"/>
-      <c r="C16" s="30" t="n"/>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="30" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="n"/>
-      <c r="B17" s="30" t="n"/>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="30" t="n"/>
-      <c r="H17" s="30" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="30" t="n"/>
-      <c r="B18" s="30" t="n"/>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="30" t="n"/>
-      <c r="H18" s="30" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="30" t="n"/>
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="30" t="n"/>
-      <c r="G19" s="30" t="n"/>
-      <c r="H19" s="30" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="30" t="n"/>
-      <c r="B20" s="30" t="n"/>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="30" t="n"/>
-      <c r="F20" s="30" t="n"/>
-      <c r="G20" s="30" t="n"/>
-      <c r="H20" s="30" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="30" t="n"/>
-      <c r="B21" s="30" t="n"/>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="30" t="n"/>
-      <c r="G21" s="30" t="n"/>
-      <c r="H21" s="30" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="30" t="n"/>
-      <c r="B22" s="30" t="n"/>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="30" t="n"/>
-      <c r="G22" s="30" t="n"/>
-      <c r="H22" s="30" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="30" t="n"/>
-      <c r="B23" s="30" t="n"/>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="30" t="n"/>
-      <c r="G23" s="30" t="n"/>
-      <c r="H23" s="30" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="30" t="n"/>
-      <c r="B24" s="30" t="n"/>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="30" t="n"/>
-      <c r="F24" s="30" t="n"/>
-      <c r="G24" s="30" t="n"/>
-      <c r="H24" s="30" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="30" t="n"/>
-      <c r="B25" s="30" t="n"/>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="30" t="n"/>
-      <c r="G25" s="30" t="n"/>
-      <c r="H25" s="30" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="30" t="n"/>
-      <c r="B26" s="30" t="n"/>
-      <c r="C26" s="30" t="n"/>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="30" t="n"/>
-      <c r="F26" s="30" t="n"/>
-      <c r="G26" s="30" t="n"/>
-      <c r="H26" s="30" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="n"/>
-      <c r="B27" s="30" t="n"/>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="30" t="n"/>
-      <c r="G27" s="30" t="n"/>
-      <c r="H27" s="30" t="n"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="3">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C7:C20">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H20">
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>H7="EKSİK"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="0">
-      <formula>H7="TAM"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <tabColor rgb="00B08948"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -12116,7 +12079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -12532,7 +12495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
@@ -12965,7 +12928,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -13272,7 +13235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -13592,7 +13555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -13822,7 +13785,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -14384,253 +14347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="88" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="89" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="89" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="89" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="89" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="89" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="89" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="90" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="91" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="82" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="92" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="90" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="91" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="82" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="92" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="90" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="91" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="82" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="92" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="90" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="91" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="82" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="92" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="90" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="91" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="82" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="92" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="90" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="91" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="82" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="92" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -14813,7 +14530,485 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B3:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="B3" s="137" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="138" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="139" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="140" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="140" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="140" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="140" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="140" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="140" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="140" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="140" t="inlineStr">
+        <is>
+          <t>DURUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="141" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="142" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="143" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="144" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="145" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="146">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="143" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="147" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="148" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="149" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="150" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="151" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="153">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="150" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="154" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="141" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="142" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="143" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="144" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="145" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="146">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="143" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="147" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="148" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="149" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="150" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="151" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="153">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="150" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="155" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="141" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="142" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="143" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="144" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="145" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="146">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="143" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="147" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="148" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="149" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="150" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="151" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="153">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="150" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="156" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="141" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="142" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="143" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="144" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="145" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="146">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="143" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="147" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="148" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="149" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="150" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="151" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="153">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="150" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="155" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="141" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="142" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="143" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="144" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="145" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="146">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="143" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="147" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="148" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="149" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="150" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="151" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="153">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="150" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="155" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="157" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="125" t="n"/>
+      <c r="D17" s="125" t="n"/>
+      <c r="E17" s="158">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="125" t="n"/>
+      <c r="G17" s="125" t="n"/>
+      <c r="H17" s="125" t="n"/>
+      <c r="I17" s="125" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -15942,7 +16137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -16144,733 +16339,319 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="88" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="93" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="159" t="inlineStr">
+        <is>
+          <t>KDV IADE LISTESI ROBOTU GIB7 — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="160" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="161" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="94" t="inlineStr">
-        <is>
-          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="162" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="100" t="n"/>
+      <c r="D6" s="100" t="n"/>
+      <c r="E6" s="100" t="n"/>
+      <c r="F6" s="100" t="n"/>
+      <c r="H6" s="163" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="100" t="n"/>
+      <c r="J6" s="100" t="n"/>
+      <c r="K6" s="100" t="n"/>
+      <c r="L6" s="100" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="100" t="n"/>
+      <c r="C7" s="100" t="n"/>
+      <c r="D7" s="100" t="n"/>
+      <c r="E7" s="100" t="n"/>
+      <c r="F7" s="100" t="n"/>
+      <c r="H7" s="100" t="n"/>
+      <c r="I7" s="100" t="n"/>
+      <c r="J7" s="100" t="n"/>
+      <c r="K7" s="100" t="n"/>
+      <c r="L7" s="100" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="164" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="100" t="n"/>
+      <c r="D8" s="100" t="n"/>
+      <c r="E8" s="165" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="100" t="n"/>
+      <c r="H8" s="164" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="100" t="n"/>
+      <c r="J8" s="100" t="n"/>
+      <c r="K8" s="166" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="100" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="93" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="164" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="100" t="n"/>
+      <c r="D9" s="100" t="n"/>
+      <c r="E9" s="167" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="100" t="n"/>
+      <c r="H9" s="164" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="100" t="n"/>
+      <c r="J9" s="100" t="n"/>
+      <c r="K9" s="167" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="100" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="94" t="inlineStr">
-        <is>
-          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="164" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="100" t="n"/>
+      <c r="D10" s="100" t="n"/>
+      <c r="E10" s="168" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="100" t="n"/>
+      <c r="H10" s="164" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="100" t="n"/>
+      <c r="J10" s="100" t="n"/>
+      <c r="K10" s="168" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="100" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="164" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="100" t="n"/>
+      <c r="D11" s="100" t="n"/>
+      <c r="E11" s="168" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="100" t="n"/>
+      <c r="H11" s="164" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="100" t="n"/>
+      <c r="J11" s="100" t="n"/>
+      <c r="K11" s="168" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="100" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="100" t="n"/>
+      <c r="C12" s="100" t="n"/>
+      <c r="D12" s="100" t="n"/>
+      <c r="E12" s="100" t="n"/>
+      <c r="F12" s="100" t="n"/>
+      <c r="H12" s="100" t="n"/>
+      <c r="I12" s="100" t="n"/>
+      <c r="J12" s="100" t="n"/>
+      <c r="K12" s="100" t="n"/>
+      <c r="L12" s="100" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="93" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="100" t="n"/>
+      <c r="C13" s="100" t="n"/>
+      <c r="D13" s="100" t="n"/>
+      <c r="E13" s="100" t="n"/>
+      <c r="F13" s="100" t="n"/>
+      <c r="H13" s="100" t="n"/>
+      <c r="I13" s="100" t="n"/>
+      <c r="J13" s="100" t="n"/>
+      <c r="K13" s="100" t="n"/>
+      <c r="L13" s="100" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="169" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="100" t="n"/>
+      <c r="D14" s="100" t="n"/>
+      <c r="E14" s="100" t="n"/>
+      <c r="F14" s="100" t="n"/>
+      <c r="H14" s="170" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="100" t="n"/>
+      <c r="J14" s="100" t="n"/>
+      <c r="K14" s="100" t="n"/>
+      <c r="L14" s="100" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="90" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="90" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="100" t="n"/>
+      <c r="C15" s="100" t="n"/>
+      <c r="D15" s="100" t="n"/>
+      <c r="E15" s="100" t="n"/>
+      <c r="F15" s="100" t="n"/>
+      <c r="H15" s="100" t="n"/>
+      <c r="I15" s="100" t="n"/>
+      <c r="J15" s="100" t="n"/>
+      <c r="K15" s="100" t="n"/>
+      <c r="L15" s="100" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="80" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="127" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="127" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="127" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="127" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000F2742"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AD29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PANO — KDV İade Listesi Robotu (GİB 7 Liste)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Yönetim paneli — KDV İade Listesi (GİB 7 Liste)</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>İndirilecek</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Yüklenilen</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>İade</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Talep</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Sapma</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>GÇB</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>İhraç</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Dağılım</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>M-SEN</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>Tahmin</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>Vaka</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="5">
-        <f>IFERROR(kil_modulT1,0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="5">
-        <f>IFERROR(kil_modulT2,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="5">
-        <f>IFERROR(kil_iadeSecili,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="5">
-        <f>IFERROR(GIRDI!B14,0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="5">
-        <f>IFERROR(kil_modulO1,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="6">
-        <f>IFERROR(MOTOR!G30,0)</f>
-        <v/>
-      </c>
-      <c r="H4" s="6">
-        <f>IFERROR(MOTOR!G31,0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="5">
-        <f>IFERROR(kil_liste3,0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="5">
-        <f>IFERROR(GIRDI!B12,0)</f>
-        <v/>
-      </c>
-      <c r="K4" s="7">
-        <f>IFERROR(kil_modulO6,0)</f>
-        <v/>
-      </c>
-      <c r="L4" s="5">
-        <f>IFERROR(kil_kuralDegisimSenaryo,0)</f>
-        <v/>
-      </c>
-      <c r="M4" s="5">
-        <f>IFERROR(SENARYO!B32,0)</f>
-        <v/>
-      </c>
-      <c r="N4" s="8">
-        <f>IFERROR(kil_vakaDurum,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>KARAR</t>
-        </is>
-      </c>
-      <c r="B6" s="9">
-        <f>kil_kararMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="B7" s="11">
-        <f>kil_kararGerekce</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>GİB 7 liste adları</t>
-        </is>
-      </c>
-      <c r="B8" s="11">
-        <f>kil_listeSayfalari</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Analitik modüller</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Kod</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Gösterge</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Makine Yorumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>İndirilecek toplam</t>
-        </is>
-      </c>
-      <c r="C12" s="16">
-        <f>IFERROR(kil_liste1,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="11">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"İndirilecek KDV ",TEXT(C12,"₺ #,##0")," TL — LISTE_1")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Yüklenilen toplam</t>
-        </is>
-      </c>
-      <c r="C13" s="16">
-        <f>IFERROR(kil_liste2,0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="11">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Yüklenilen KDV ",TEXT(C13,"₺ #,##0")," TL — LISTE_2")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>İade sapması</t>
-        </is>
-      </c>
-      <c r="C14" s="16">
-        <f>IFERROR(MOTOR!G26,0)</f>
-        <v/>
-      </c>
-      <c r="D14" s="11">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"|Seçili−talep| ",TEXT(C14,"₺ #,##0")," TL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Tornado max etki</t>
-        </is>
-      </c>
-      <c r="C15" s="17">
-        <f>IFERROR(kil_duyarlilikSira,"-")</f>
-        <v/>
-      </c>
-      <c r="D15" s="11">
-        <f>IFERROR(kil_yorumDuyarlilik,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>O3</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Senaryo bant</t>
-        </is>
-      </c>
-      <c r="C16" s="16">
-        <f>IFERROR(kil_senaryoKarsilastirma,0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="11">
-        <f>IFERROR(kil_yorumSenaryo,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>O6</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Liste dağılımı</t>
-        </is>
-      </c>
-      <c r="C17" s="18">
-        <f>IFERROR(MOTOR!G55,0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="11">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"İndirilecek/yüklenen ",TEXT(C17,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>O8</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Kalite skoru</t>
-        </is>
-      </c>
-      <c r="C18" s="16">
-        <f>IFERROR(MOTOR!G52,0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="11">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Kalite ",TEXT(C18,"0")," puan")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>M_SEN</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>M-SEN iade</t>
-        </is>
-      </c>
-      <c r="C19" s="16">
-        <f>IFERROR(kil_kuralDegisimSenaryo,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="11">
-        <f>IFERROR(kil_yorumKuralDegisim,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Tahmin aralık</t>
-        </is>
-      </c>
-      <c r="C20" s="16">
-        <f>IFERROR(kil_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="D20" s="11">
-        <f>IFERROR(kil_yorumTahmin,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Senaryo iade P90</t>
-        </is>
-      </c>
-      <c r="C21" s="16">
-        <f>IFERROR(IF(COUNT(SENARYO!C6:C9)&lt;2,0,_xlfn.PERCENTILE.INC(SENARYO!C6:C9,kil_yuzdelikOran)),0)</f>
-        <v/>
-      </c>
-      <c r="D21" s="11">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"P90 iade ",TEXT(C21,"₺ #,##0")," TL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Liste</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Tutar</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Kalem</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>Tutar</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>LISTE_1 İndirilecek</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="n">
-        <v>800000</v>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>Seçili iade</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>LISTE_2 Yüklenilen</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>İade talep</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="n">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>LISTE_3 GÇB</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>İade A</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>LISTE_4 Satış</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>İade B</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>LISTE_6 İade</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>M-SEN iade</t>
-        </is>
-      </c>
-      <c r="E29" s="20" t="n">
-        <v>1050000</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="3">
-    <mergeCell ref="B8:N8"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>ISNUMBER(SEARCH("İADE",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>ISNUMBER(SEARCH("EKSİK",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>ISNUMBER(SEARCH("BEKLE",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="1">
-      <formula>ISNUMBER(SEARCH("VERİ YOK",B6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="5">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="7" operator="between" dxfId="3">
-      <formula>50</formula>
-      <formula>79</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="4">
-      <formula>50</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="17" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="cellIs" priority="9" operator="greaterThanOrEqual" dxfId="4">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="between" dxfId="3">
-      <formula>40</formula>
-      <formula>69</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="5">
-      <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4">
-    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="cellIs" priority="19" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J4">
-    <cfRule type="cellIs" priority="20" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K4">
-    <cfRule type="cellIs" priority="21" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4">
-    <cfRule type="cellIs" priority="22" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M4">
-    <cfRule type="cellIs" priority="23" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N4">
-    <cfRule type="cellIs" priority="24" operator="lessThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LKDV İade Listesi Robotu (GİB 7 Liste) · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LKDV İade Listesi Robotu (GİB 7 Liste) · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B08948"/>
@@ -18060,7 +17841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F7A4D"/>
@@ -18504,7 +18285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008064A2"/>
@@ -20328,7 +20109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -20551,6 +20332,437 @@
       </c>
       <c r="M9" s="20" t="n">
         <v>100000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="n"/>
+      <c r="B10" s="30" t="n"/>
+      <c r="C10" s="30" t="n"/>
+      <c r="D10" s="30" t="n"/>
+      <c r="E10" s="30" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
+      <c r="H10" s="30" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="30" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+      <c r="H11" s="30" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="n"/>
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="30" t="n"/>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="30" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
+      <c r="H12" s="30" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="30" t="n"/>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="30" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+      <c r="H13" s="30" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="n"/>
+      <c r="B14" s="30" t="n"/>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="30" t="n"/>
+      <c r="E14" s="30" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+      <c r="H14" s="30" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+      <c r="H15" s="30" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="n"/>
+      <c r="B16" s="30" t="n"/>
+      <c r="C16" s="30" t="n"/>
+      <c r="D16" s="30" t="n"/>
+      <c r="E16" s="30" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+      <c r="H16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="30" t="n"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="30" t="n"/>
+      <c r="E17" s="30" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+      <c r="H17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="30" t="n"/>
+      <c r="C18" s="30" t="n"/>
+      <c r="D18" s="30" t="n"/>
+      <c r="E18" s="30" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+      <c r="H18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="30" t="n"/>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="30" t="n"/>
+      <c r="E19" s="30" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+      <c r="H19" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="n"/>
+      <c r="B20" s="30" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="30" t="n"/>
+      <c r="E20" s="30" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+      <c r="H20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="30" t="n"/>
+      <c r="C21" s="30" t="n"/>
+      <c r="D21" s="30" t="n"/>
+      <c r="E21" s="30" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+      <c r="H21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="30" t="n"/>
+      <c r="C22" s="30" t="n"/>
+      <c r="D22" s="30" t="n"/>
+      <c r="E22" s="30" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+      <c r="H22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="30" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+      <c r="H23" s="30" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="n"/>
+      <c r="B24" s="30" t="n"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="30" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+      <c r="H24" s="30" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="30" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="30" t="n"/>
+      <c r="E25" s="30" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+      <c r="H25" s="30" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="n"/>
+      <c r="B26" s="30" t="n"/>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="30" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+      <c r="H26" s="30" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="n"/>
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="30" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
+      <c r="H27" s="30" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="3">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C7:C20">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H20">
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>H7="EKSİK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>H7="TAM"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LISTE 2 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="36" t="inlineStr">
+        <is>
+          <t>LISTE_2: Yüklenilen KDV Listesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Sarı satırlar manuel satır girişi; canlı özet MOTOR'dan gelir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Satır Numarası</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Belge/Kalem</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Tutar</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>KDV</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Kaynak</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Durum</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Not</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>Kontrol</t>
+        </is>
+      </c>
+      <c r="M6" s="46" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="48" t="inlineStr">
+        <is>
+          <t>Yüklenen kalem Y1</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D7" s="49" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E7" s="48" t="inlineStr">
+        <is>
+          <t>GIRDI</t>
+        </is>
+      </c>
+      <c r="F7" s="48" t="inlineStr">
+        <is>
+          <t>TAM</t>
+        </is>
+      </c>
+      <c r="G7" s="48" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="H7" s="48" t="inlineStr">
+        <is>
+          <t>TAM</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Canlı yüklenilen (MOTOR)</t>
+        </is>
+      </c>
+      <c r="K7" s="28">
+        <f>IFERROR(kil_liste2,0)</f>
+        <v/>
+      </c>
+      <c r="M7" s="20" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>Yüklenen kalem Y2</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="n">
+        <v>700000</v>
+      </c>
+      <c r="D8" s="49" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E8" s="48" t="inlineStr">
+        <is>
+          <t>GIRDI</t>
+        </is>
+      </c>
+      <c r="F8" s="48" t="inlineStr">
+        <is>
+          <t>TAM</t>
+        </is>
+      </c>
+      <c r="G8" s="48" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="H8" s="48" t="inlineStr">
+        <is>
+          <t>TAM</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>LISTE_2 özet metni</t>
+        </is>
+      </c>
+      <c r="K8" s="11">
+        <f>IFERROR(_xlfn.TEXTJOIN(" | ",TRUE,"LISTE_2","Yüklenilen KDV Listesi","Özet=",TEXT(K7,"₺ #,##0")),"-")</f>
+        <v/>
+      </c>
+      <c r="M8" s="20" t="n">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>Yüklenen kalem Y3</t>
+        </is>
+      </c>
+      <c r="C9" s="49" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D9" s="49" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E9" s="48" t="inlineStr">
+        <is>
+          <t>GIRDI</t>
+        </is>
+      </c>
+      <c r="F9" s="48" t="inlineStr">
+        <is>
+          <t>TAM</t>
+        </is>
+      </c>
+      <c r="G9" s="48" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="H9" s="48" t="inlineStr">
+        <is>
+          <t>TAM</t>
+        </is>
+      </c>
+      <c r="M9" s="20" t="n">
+        <v>300000</v>
       </c>
     </row>
     <row r="10">
@@ -20762,7 +20974,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -20784,14 +20996,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LISTE 2 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
+          <t>LISTE 3 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="36" t="inlineStr">
         <is>
-          <t>LISTE_2: Yüklenilen KDV Listesi</t>
+          <t>LISTE_3: GÇB Listesi</t>
         </is>
       </c>
     </row>
@@ -20855,14 +21067,14 @@
       </c>
       <c r="B7" s="48" t="inlineStr">
         <is>
-          <t>Yüklenen kalem Y1</t>
+          <t>GÇB-2026-001</t>
         </is>
       </c>
       <c r="C7" s="49" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D7" s="49" t="n">
-        <v>200000</v>
+        <v>2000000</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>0</v>
       </c>
       <c r="E7" s="48" t="inlineStr">
         <is>
@@ -20876,7 +21088,7 @@
       </c>
       <c r="G7" s="48" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>Hasılat</t>
         </is>
       </c>
       <c r="H7" s="48" t="inlineStr">
@@ -20886,15 +21098,15 @@
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>Canlı yüklenilen (MOTOR)</t>
+          <t>Canlı GÇB (MOTOR)</t>
         </is>
       </c>
       <c r="K7" s="28">
-        <f>IFERROR(kil_liste2,0)</f>
+        <f>IFERROR(kil_liste3,0)</f>
         <v/>
       </c>
       <c r="M7" s="20" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="8">
@@ -20903,14 +21115,14 @@
       </c>
       <c r="B8" s="48" t="inlineStr">
         <is>
-          <t>Yüklenen kalem Y2</t>
+          <t>GÇB-2026-002</t>
         </is>
       </c>
       <c r="C8" s="49" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D8" s="49" t="n">
-        <v>140000</v>
+        <v>1500000</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="48" t="inlineStr">
         <is>
@@ -20924,7 +21136,7 @@
       </c>
       <c r="G8" s="48" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>Hasılat</t>
         </is>
       </c>
       <c r="H8" s="48" t="inlineStr">
@@ -20934,15 +21146,15 @@
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>LISTE_2 özet metni</t>
+          <t>LISTE_3 özet metni</t>
         </is>
       </c>
       <c r="K8" s="11">
-        <f>IFERROR(_xlfn.TEXTJOIN(" | ",TRUE,"LISTE_2","Yüklenilen KDV Listesi","Özet=",TEXT(K7,"₺ #,##0")),"-")</f>
+        <f>IFERROR(_xlfn.TEXTJOIN(" | ",TRUE,"LISTE_3","GÇB Listesi","Özet=",TEXT(K7,"₺ #,##0")),"-")</f>
         <v/>
       </c>
       <c r="M8" s="20" t="n">
-        <v>700000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="9">
@@ -20951,14 +21163,14 @@
       </c>
       <c r="B9" s="48" t="inlineStr">
         <is>
-          <t>Yüklenen kalem Y3</t>
+          <t>GÇB-2026-003</t>
         </is>
       </c>
       <c r="C9" s="49" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D9" s="49" t="n">
-        <v>60000</v>
+        <v>1000000</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>0</v>
       </c>
       <c r="E9" s="48" t="inlineStr">
         <is>
@@ -20972,7 +21184,7 @@
       </c>
       <c r="G9" s="48" t="inlineStr">
         <is>
-          <t>Demo</t>
+          <t>Hasılat</t>
         </is>
       </c>
       <c r="H9" s="48" t="inlineStr">
@@ -20981,7 +21193,7 @@
         </is>
       </c>
       <c r="M9" s="20" t="n">
-        <v>300000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="10">

--- a/EXCELARSIV_PRODUCTS/kdv-iade-listesi-robotu-gib7/KdvIadeListesiRobotuGib7.xlsx
+++ b/EXCELARSIV_PRODUCTS/kdv-iade-listesi-robotu-gib7/KdvIadeListesiRobotuGib7.xlsx
@@ -110,13 +110,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="85">
     <font>
@@ -1160,7 +1161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1645,6 +1646,24 @@
     </xf>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="44" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="47" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="48" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="51" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="52" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="70" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="67" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="67" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -17549,7 +17568,7 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
@@ -17565,7 +17584,7 @@
     <row r="2">
       <c r="B2" s="95" t="inlineStr">
         <is>
-          <t>KDV IADE LISTESI ROBOTU GIB7 — YÖNETİM VE KARAR SİSTEMİ</t>
+          <t>KDV İADE LISTESI ROBOTU (GİB 7 LISTE)</t>
         </is>
       </c>
       <c r="L2" s="96" t="inlineStr">
@@ -17582,36 +17601,36 @@
     <row r="3">
       <c r="B3" s="98" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: SMMM, YMM, mali işler, ihracatçı · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="99" t="inlineStr">
         <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
+          <t>İNDIRILECEK TOPLAM</t>
         </is>
       </c>
       <c r="C5" s="100" t="n"/>
       <c r="D5" s="101" t="inlineStr">
         <is>
-          <t>DOĞRULANMIŞ</t>
+          <t>KONSOLİDE</t>
         </is>
       </c>
       <c r="E5" s="102" t="inlineStr">
         <is>
-          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+          <t>YÜKLENILEN TOPLAM</t>
         </is>
       </c>
       <c r="F5" s="100" t="n"/>
       <c r="G5" s="103" t="inlineStr">
         <is>
-          <t>MİNİMUM</t>
+          <t>KONTROL</t>
         </is>
       </c>
       <c r="H5" s="99" t="inlineStr">
         <is>
-          <t>OPERASYONEL NET MARJ</t>
+          <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
       <c r="I5" s="100" t="n"/>
@@ -17647,31 +17666,27 @@
       <c r="M6" s="100" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="109" t="inlineStr">
-        <is>
-          <t>₺28.450.000</t>
-        </is>
+      <c r="B7" s="196">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="100" t="n"/>
       <c r="D7" s="100" t="n"/>
-      <c r="E7" s="110" t="inlineStr">
-        <is>
-          <t>₺940.000</t>
-        </is>
+      <c r="E7" s="197">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="100" t="n"/>
       <c r="G7" s="100" t="n"/>
-      <c r="H7" s="109" t="inlineStr">
-        <is>
-          <t>₺8.120.000</t>
-        </is>
+      <c r="H7" s="196">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="100" t="n"/>
       <c r="J7" s="100" t="n"/>
-      <c r="K7" s="111" t="inlineStr">
-        <is>
-          <t>98/100</t>
-        </is>
+      <c r="K7" s="111">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="100" t="n"/>
       <c r="M7" s="100" t="n"/>
@@ -17693,28 +17708,28 @@
     <row r="9">
       <c r="B9" s="112" t="inlineStr">
         <is>
-          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="100" t="n"/>
       <c r="D9" s="100" t="n"/>
       <c r="E9" s="113" t="inlineStr">
         <is>
-          <t>● Tüm riskli kayıtlar kontrol altında</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="100" t="n"/>
       <c r="G9" s="100" t="n"/>
       <c r="H9" s="112" t="inlineStr">
         <is>
-          <t>██████████░░░░░ %28.5 NET MARJ</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="100" t="n"/>
       <c r="J9" s="100" t="n"/>
       <c r="K9" s="114" t="inlineStr">
         <is>
-          <t>✓ 0 Formül ve Döngüsel Hata</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="100" t="n"/>
@@ -17723,7 +17738,7 @@
     <row r="11">
       <c r="B11" s="93" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>KDV İADE LISTESI ROBOTU (GİB 7 LISTE) — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="115" t="inlineStr">
@@ -17740,7 +17755,7 @@
     <row r="12">
       <c r="B12" s="92" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="92" t="inlineStr">
@@ -17813,18 +17828,16 @@
       </c>
       <c r="H15" s="118" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="118" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="119" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="198">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="199">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="120" t="inlineStr">
         <is>
@@ -17854,18 +17867,16 @@
       </c>
       <c r="H16" s="118" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="118" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="119" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="198">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="199">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="120" t="inlineStr">
         <is>
@@ -17895,18 +17906,16 @@
       </c>
       <c r="H17" s="118" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="118" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="119" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="198">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="199">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="120" t="inlineStr">
         <is>
@@ -17936,18 +17945,16 @@
       </c>
       <c r="H18" s="118" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="118" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="119" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="198">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="199">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="120" t="inlineStr">
         <is>
@@ -17980,15 +17987,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="123" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="124" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="200">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="201">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="125" t="inlineStr"/>
       <c r="L19" s="126" t="inlineStr">
@@ -18050,7 +18055,7 @@
       </c>
       <c r="K23" s="131" t="inlineStr">
         <is>
-          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
         </is>
       </c>
       <c r="L23" s="129" t="n"/>
@@ -18074,7 +18079,7 @@
       </c>
       <c r="K24" s="132" t="inlineStr">
         <is>
-          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
         </is>
       </c>
     </row>
@@ -21509,7 +21514,7 @@
     <row r="3">
       <c r="B3" s="137" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  KDV İADE LISTESI ROBOTU (GİB 7 LISTE) — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="138" t="inlineStr">
@@ -21578,10 +21583,10 @@
       </c>
       <c r="D6" s="143" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="144" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="202" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="145" t="n">
@@ -21615,10 +21620,10 @@
       </c>
       <c r="D7" s="150" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="151" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="202" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="152" t="n">
@@ -21652,10 +21657,10 @@
       </c>
       <c r="D8" s="143" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="144" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="202" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="145" t="n">
@@ -21689,10 +21694,10 @@
       </c>
       <c r="D9" s="150" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="151" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="202" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="152" t="n">
@@ -21726,10 +21731,10 @@
       </c>
       <c r="D10" s="143" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="144" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="202" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="145" t="n">
@@ -21763,10 +21768,10 @@
       </c>
       <c r="D11" s="150" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="151" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="202" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="152" t="n">
@@ -21778,7 +21783,7 @@
       </c>
       <c r="H11" s="150" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="156" t="inlineStr">
@@ -21800,10 +21805,10 @@
       </c>
       <c r="D12" s="143" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="144" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="202" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="145" t="n">
@@ -21815,7 +21820,7 @@
       </c>
       <c r="H12" s="143" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="147" t="inlineStr">
@@ -21837,10 +21842,10 @@
       </c>
       <c r="D13" s="150" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="151" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="202" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="152" t="n">
@@ -21874,10 +21879,10 @@
       </c>
       <c r="D14" s="143" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="144" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="202" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="145" t="n">
@@ -21911,10 +21916,10 @@
       </c>
       <c r="D15" s="150" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="151" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="202" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="152" t="n">
@@ -21998,14 +22003,14 @@
     <row r="2">
       <c r="B2" s="159" t="inlineStr">
         <is>
-          <t>KDV IADE LISTESI ROBOTU GIB7 — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>KDV İADE LISTESI ROBOTU (GİB 7 LISTE) — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="160" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · SMMM, YMM, mali işler, ihracatçı</t>
         </is>
       </c>
     </row>
@@ -22084,10 +22089,9 @@
       </c>
       <c r="C9" s="100" t="n"/>
       <c r="D9" s="100" t="n"/>
-      <c r="E9" s="167" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="203">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="100" t="n"/>
       <c r="H9" s="164" t="inlineStr">
@@ -22097,10 +22101,9 @@
       </c>
       <c r="I9" s="100" t="n"/>
       <c r="J9" s="100" t="n"/>
-      <c r="K9" s="167" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="203">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="100" t="n"/>
     </row>
@@ -22112,10 +22115,9 @@
       </c>
       <c r="C10" s="100" t="n"/>
       <c r="D10" s="100" t="n"/>
-      <c r="E10" s="168" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="204">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="100" t="n"/>
       <c r="H10" s="164" t="inlineStr">
@@ -22125,10 +22127,9 @@
       </c>
       <c r="I10" s="100" t="n"/>
       <c r="J10" s="100" t="n"/>
-      <c r="K10" s="168" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="204">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="100" t="n"/>
     </row>
@@ -22140,10 +22141,9 @@
       </c>
       <c r="C11" s="100" t="n"/>
       <c r="D11" s="100" t="n"/>
-      <c r="E11" s="168" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="205">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="100" t="n"/>
       <c r="H11" s="164" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/kdv-iade-listesi-robotu-gib7/KdvIadeListesiRobotuGib7.xlsx
+++ b/EXCELARSIV_PRODUCTS/kdv-iade-listesi-robotu-gib7/KdvIadeListesiRobotuGib7.xlsx
@@ -119,7 +119,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="85">
+  <fonts count="87">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -606,8 +606,20 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -791,6 +803,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1161,7 +1179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1664,6 +1682,30 @@
     </xf>
     <xf numFmtId="170" fontId="67" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10659,20 +10701,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="147.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="172" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="173" t="inlineStr">
         <is>
@@ -10937,6 +10996,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="176" t="inlineStr">
         <is>
@@ -11035,7 +11095,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11057,17 +11117,30 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>GIRDI — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>Dönem ve GİB 7 liste girdileri</t>
         </is>
@@ -11253,6 +11326,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -11275,6 +11349,9 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -12132,6 +12209,909 @@
         <v/>
       </c>
     </row>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+    <row r="1001"/>
+    <row r="1002"/>
+    <row r="1003"/>
+    <row r="1004"/>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
     <row r="1024" ht="20" customHeight="1">
       <c r="A1024" s="34" t="inlineStr">
         <is>
@@ -12141,9 +13121,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A1024:AN1024"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B9:B14">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
@@ -12254,15 +13235,24 @@
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>KURALLAR — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>GİB iade kural tablosu (yıl yan yana)</t>
         </is>
@@ -12275,6 +13265,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -12582,6 +13573,8 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -12625,9 +13618,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <conditionalFormatting sqref="F7:F11">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
@@ -12692,17 +13685,29 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>MOTOR — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>Hesap zinciri — her adımda kural_id</t>
         </is>
@@ -12715,6 +13720,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -14468,6 +15474,7 @@
         <v/>
       </c>
     </row>
+    <row r="59"/>
     <row r="60">
       <c r="I60" s="22" t="inlineStr">
         <is>
@@ -14478,8 +15485,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <conditionalFormatting sqref="G7:G70">
@@ -14517,19 +15524,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>LISTE 1 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>LISTE_1: İndirilecek KDV Listesi</t>
         </is>
@@ -14542,6 +15559,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -14907,9 +15925,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C20">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
@@ -14948,19 +15966,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>LISTE 2 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>LISTE_2: Yüklenilen KDV Listesi</t>
         </is>
@@ -14973,6 +16001,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -15338,9 +16367,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C20">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
@@ -15379,19 +16408,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>LISTE 3 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>LISTE_3: GÇB Listesi</t>
         </is>
@@ -15404,6 +16443,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -15769,9 +16809,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C20">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
@@ -15810,19 +16850,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>LISTE 4 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>LISTE_4: Satış Faturaları Listesi</t>
         </is>
@@ -15835,6 +16885,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -16186,9 +17237,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C20">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
@@ -16226,19 +17277,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>LISTE 5 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>LISTE_5: Alış Faturaları Listesi</t>
         </is>
@@ -16251,6 +17312,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -16602,9 +17664,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C20">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
@@ -16642,19 +17704,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>LISTE 6 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>LISTE_6: İade Hesap Cetveli</t>
         </is>
@@ -16667,6 +17739,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -17110,9 +18183,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C20">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
@@ -17151,19 +18224,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>LISTE 7 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>LISTE_7: Ek Belge / Tamamlayıcı Liste</t>
         </is>
@@ -17176,6 +18259,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -17527,9 +18611,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C20">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
@@ -17556,22 +18640,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="72.5" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="36.5" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="11.5" customWidth="1" min="7" max="7"/>
+    <col width="75.5" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15.5" customWidth="1" min="10" max="10"/>
+    <col width="81.5" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17605,6 +18690,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="99" t="inlineStr">
         <is>
@@ -17735,6 +18821,7 @@
       <c r="L9" s="100" t="n"/>
       <c r="M9" s="100" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="93" t="inlineStr">
         <is>
@@ -17764,6 +18851,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="116" t="inlineStr">
         <is>
@@ -18018,6 +19106,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="127" t="inlineStr">
         <is>
@@ -18106,13 +19195,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="208" t="n"/>
+      <c r="H26" s="208" t="n"/>
+      <c r="I26" s="209" t="n"/>
       <c r="K26" s="136" t="inlineStr">
         <is>
           <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="210" t="n"/>
+      <c r="G27" s="211" t="n"/>
+      <c r="H27" s="211" t="n"/>
+      <c r="I27" s="212" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -18133,28 +19230,42 @@
   <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="50.5" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>SENARYO — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>Senaryo ve duyarlılık</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="46" t="inlineStr">
         <is>
@@ -18270,6 +19381,7 @@
         <v>1050000</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
@@ -18292,6 +19404,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
@@ -18397,6 +19510,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -18419,6 +19533,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
@@ -18529,9 +19644,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B12:H12"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="C6:C9">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
@@ -18566,30 +19682,46 @@
   <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="1" max="1"/>
+    <col width="41.5" customWidth="1" min="2" max="2"/>
+    <col width="43.5" customWidth="1" min="3" max="3"/>
+    <col width="18.5" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="16.5" customWidth="1" min="10" max="10"/>
+    <col width="13.5" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>VAKALAR — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+      <c r="J1" s="207" t="n"/>
+      <c r="K1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>GİB iade altın vakaları</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
@@ -18814,6 +19946,8 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -18839,8 +19973,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:G9">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -18870,26 +20004,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="97.5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>KANIT RAPORU — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="58" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>KANIT RAPORU — KDV İade Listesi (GİB 7 Liste)</t>
         </is>
@@ -18928,6 +20075,7 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
@@ -19012,6 +20160,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
@@ -19074,6 +20223,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -19085,6 +20235,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
@@ -19107,6 +20258,7 @@
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
@@ -19118,6 +20270,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
@@ -19134,6 +20287,7 @@
       </c>
       <c r="B32" s="25" t="inlineStr"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="61" t="inlineStr">
         <is>
@@ -19146,10 +20300,10 @@
   <mergeCells count="8">
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B22:F22"/>
-    <mergeCell ref="A3:F3"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
   </mergeCells>
@@ -19194,23 +20348,41 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="55.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>KONTROLLER — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>Canlı kontrol paneli</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
@@ -19354,6 +20526,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
@@ -19389,8 +20562,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B14">
     <cfRule type="expression" priority="1" dxfId="1">
@@ -19423,27 +20597,38 @@
   <dimension ref="A1:AD25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18.5" customWidth="1" min="1" max="1"/>
+    <col width="15.5" customWidth="1" min="2" max="2"/>
+    <col width="14.5" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15.5" customWidth="1" min="6" max="6"/>
+    <col width="14.5" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15.5" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>ORNEK VERI — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+      <c r="J1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>Örnek senaryo kütüphanesi</t>
         </is>
@@ -19921,8 +21106,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B20">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
@@ -19982,29 +21167,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="33.5" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>LISTELER — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>Doğrulama listeleri</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="46" t="inlineStr">
         <is>
@@ -20057,6 +21258,7 @@
         <v>2027</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
@@ -20150,8 +21352,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:T1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -20169,29 +21372,39 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="64.5" customWidth="1" min="2" max="2"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
+    <col width="39.5" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="19.5" customWidth="1" min="6" max="6"/>
+    <col width="20.5" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>AYARLAR — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="225" t="inlineStr">
         <is>
           <t>Parametreler (tek kaynak)</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
@@ -21252,6 +22465,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="B33" s="66" t="inlineStr">
         <is>
@@ -21259,6 +22473,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="B35" s="61" t="inlineStr">
         <is>
@@ -21268,8 +22483,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="2025-2027." promptTitle="Hesap Yılı" prompt="Aktif yılı seçin." type="list" errorStyle="stop">
@@ -21297,17 +22513,34 @@
   <dimension ref="A1:AD28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="110.5" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>KILAVUZ — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
         <is>
@@ -21315,6 +22548,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="43" t="inlineStr">
         <is>
@@ -21343,6 +22577,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
@@ -21399,6 +22634,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="67" t="inlineStr">
         <is>
@@ -21413,6 +22649,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -21437,6 +22674,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
@@ -21451,6 +22689,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="69" t="inlineStr">
         <is>
@@ -21475,9 +22714,9 @@
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A16:T16"/>
     <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A13:T13"/>
     <mergeCell ref="A11:T11"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21490,18 +22729,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="36.5" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="37.5" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22.5" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21511,12 +22751,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="137" t="inlineStr">
         <is>
           <t>🔍  KDV İADE LISTESI ROBOTU (GİB 7 LISTE) — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="213" t="n"/>
+      <c r="D3" s="213" t="n"/>
+      <c r="E3" s="214" t="n"/>
       <c r="G3" s="138" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -21528,6 +22772,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="140" t="inlineStr">
         <is>
@@ -21940,22 +23185,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="157" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="125" t="n"/>
-      <c r="D17" s="125" t="n"/>
       <c r="E17" s="158">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="125" t="n"/>
-      <c r="G17" s="125" t="n"/>
-      <c r="H17" s="125" t="n"/>
-      <c r="I17" s="125" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -21976,7 +23216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -22021,25 +23261,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="162" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="100" t="n"/>
-      <c r="D6" s="100" t="n"/>
-      <c r="E6" s="100" t="n"/>
-      <c r="F6" s="100" t="n"/>
+      <c r="C6" s="213" t="n"/>
+      <c r="D6" s="213" t="n"/>
+      <c r="E6" s="213" t="n"/>
+      <c r="F6" s="214" t="n"/>
       <c r="H6" s="163" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="100" t="n"/>
-      <c r="J6" s="100" t="n"/>
-      <c r="K6" s="100" t="n"/>
-      <c r="L6" s="100" t="n"/>
+      <c r="I6" s="213" t="n"/>
+      <c r="J6" s="213" t="n"/>
+      <c r="K6" s="213" t="n"/>
+      <c r="L6" s="214" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="100" t="n"/>
@@ -22190,32 +23431,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="100" t="n"/>
-      <c r="D14" s="100" t="n"/>
-      <c r="E14" s="100" t="n"/>
-      <c r="F14" s="100" t="n"/>
+      <c r="C14" s="215" t="n"/>
+      <c r="D14" s="215" t="n"/>
+      <c r="E14" s="215" t="n"/>
+      <c r="F14" s="216" t="n"/>
       <c r="H14" s="170" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="100" t="n"/>
-      <c r="J14" s="100" t="n"/>
-      <c r="K14" s="100" t="n"/>
-      <c r="L14" s="100" t="n"/>
+      <c r="I14" s="217" t="n"/>
+      <c r="J14" s="217" t="n"/>
+      <c r="K14" s="217" t="n"/>
+      <c r="L14" s="218" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="100" t="n"/>
-      <c r="C15" s="100" t="n"/>
-      <c r="D15" s="100" t="n"/>
-      <c r="E15" s="100" t="n"/>
-      <c r="F15" s="100" t="n"/>
-      <c r="H15" s="100" t="n"/>
-      <c r="I15" s="100" t="n"/>
-      <c r="J15" s="100" t="n"/>
-      <c r="K15" s="100" t="n"/>
-      <c r="L15" s="100" t="n"/>
-    </row>
+      <c r="B15" s="219" t="n"/>
+      <c r="C15" s="220" t="n"/>
+      <c r="D15" s="220" t="n"/>
+      <c r="E15" s="220" t="n"/>
+      <c r="F15" s="221" t="n"/>
+      <c r="H15" s="222" t="n"/>
+      <c r="I15" s="223" t="n"/>
+      <c r="J15" s="223" t="n"/>
+      <c r="K15" s="223" t="n"/>
+      <c r="L15" s="224" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="80" t="inlineStr">
         <is>
@@ -22223,6 +23465,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="127" t="inlineStr">
         <is>
@@ -22297,25 +23540,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30.5" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="3" max="3"/>
+    <col width="48.5" customWidth="1" min="4" max="4"/>
+    <col width="43.5" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="177" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="178" t="inlineStr">
         <is>
@@ -22775,7 +24030,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22788,22 +24043,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="89.5" customWidth="1" min="2" max="2"/>
+    <col width="34.5" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="180" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="181" t="inlineStr">
         <is>
@@ -23515,7 +24785,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23528,24 +24798,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30.5" customWidth="1" min="1" max="1"/>
+    <col width="71.5" customWidth="1" min="2" max="2"/>
+    <col width="160.5" customWidth="1" min="3" max="3"/>
+    <col width="70.5" customWidth="1" min="4" max="4"/>
+    <col width="50.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="185" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="186" t="inlineStr">
         <is>
@@ -24188,7 +25471,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24201,24 +25484,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
+    <col width="60.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="40.5" customWidth="1" min="4" max="4"/>
+    <col width="39.5" customWidth="1" min="5" max="5"/>
+    <col width="27.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="189" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="190" t="inlineStr">
         <is>
@@ -24733,7 +26029,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24746,23 +26042,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20.5" customWidth="1" min="1" max="1"/>
+    <col width="41.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="35.5" customWidth="1" min="4" max="4"/>
+    <col width="33.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="192" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="206" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="207" t="n"/>
+      <c r="C1" s="207" t="n"/>
+      <c r="D1" s="207" t="n"/>
+      <c r="E1" s="207" t="n"/>
+      <c r="F1" s="207" t="n"/>
+      <c r="G1" s="207" t="n"/>
+      <c r="H1" s="207" t="n"/>
+      <c r="I1" s="207" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="193" t="inlineStr">
         <is>
@@ -25309,7 +26619,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/kdv-iade-listesi-robotu-gib7/KdvIadeListesiRobotuGib7.xlsx
+++ b/EXCELARSIV_PRODUCTS/kdv-iade-listesi-robotu-gib7/KdvIadeListesiRobotuGib7.xlsx
@@ -10701,7 +10701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10722,14 +10722,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -11129,14 +11121,6 @@
           <t>GIRDI — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -13219,7 +13203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -13241,14 +13225,6 @@
           <t>KURALLAR — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -13675,7 +13651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD60"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13696,14 +13672,6 @@
           <t>MOTOR — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -15513,7 +15481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15535,14 +15503,6 @@
           <t>LISTE 1 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -15955,7 +15915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15977,14 +15937,6 @@
           <t>LISTE 2 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -16397,7 +16349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16419,14 +16371,6 @@
           <t>LISTE 3 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -16839,7 +16783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16861,14 +16805,6 @@
           <t>LISTE 4 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -17266,7 +17202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17288,14 +17224,6 @@
           <t>LISTE 5 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -17693,7 +17621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD29"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17715,14 +17643,6 @@
           <t>LISTE 6 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -18213,7 +18133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18235,14 +18155,6 @@
           <t>LISTE 7 — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -18640,7 +18552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18771,7 +18683,7 @@
       <c r="I7" s="100" t="n"/>
       <c r="J7" s="100" t="n"/>
       <c r="K7" s="111">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="100" t="n"/>
@@ -19076,11 +18988,11 @@
         </is>
       </c>
       <c r="I19" s="200">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="201">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="125" t="inlineStr"/>
@@ -19227,7 +19139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50.5" customWidth="1" min="1" max="1"/>
@@ -19248,14 +19160,6 @@
           <t>SENARYO — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -19679,7 +19583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.5" customWidth="1" min="1" max="1"/>
@@ -19702,16 +19606,6 @@
           <t>VAKALAR — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
-      <c r="J1" s="207" t="n"/>
-      <c r="K1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -20004,7 +19898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="97.5" customWidth="1" min="1" max="1"/>
@@ -20025,14 +19919,6 @@
           <t>KANIT RAPORU — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -20344,7 +20230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -20365,14 +20251,6 @@
           <t>KONTROLLER — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -20594,7 +20472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.5" customWidth="1" min="1" max="1"/>
@@ -20616,15 +20494,6 @@
           <t>ORNEK VERI — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
-      <c r="J1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -21167,7 +21036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.5" customWidth="1" min="1" max="1"/>
@@ -21188,14 +21057,6 @@
           <t>LISTELER — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -21368,7 +21229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD35"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -21388,13 +21249,6 @@
           <t>AYARLAR — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -22510,7 +22364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD28"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110.5" customWidth="1" min="1" max="1"/>
@@ -22531,14 +22385,6 @@
           <t>KILAVUZ — KDV İade Listesi Robotu (GİB 7 Liste)</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -22711,12 +22557,12 @@
     <mergeCell ref="A7:T7"/>
     <mergeCell ref="B23:J23"/>
     <mergeCell ref="A20:T20"/>
-    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A16:T16"/>
     <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A13:T13"/>
     <mergeCell ref="A11:T11"/>
+    <mergeCell ref="A19:J19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22729,7 +22575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23193,7 +23039,7 @@
         </is>
       </c>
       <c r="E17" s="158">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -23216,7 +23062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23383,7 +23229,7 @@
       <c r="C11" s="100" t="n"/>
       <c r="D11" s="100" t="n"/>
       <c r="E11" s="205">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="100" t="n"/>
@@ -23540,7 +23386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23561,14 +23407,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -24043,7 +23881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24064,14 +23902,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -24798,7 +24628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" min="1" max="1"/>
@@ -24819,14 +24649,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -25484,7 +25306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -25505,14 +25327,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -26042,7 +25856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" min="1" max="1"/>
@@ -26063,14 +25877,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="207" t="n"/>
-      <c r="C1" s="207" t="n"/>
-      <c r="D1" s="207" t="n"/>
-      <c r="E1" s="207" t="n"/>
-      <c r="F1" s="207" t="n"/>
-      <c r="G1" s="207" t="n"/>
-      <c r="H1" s="207" t="n"/>
-      <c r="I1" s="207" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">

--- a/EXCELARSIV_PRODUCTS/kdv-iade-listesi-robotu-gib7/KdvIadeListesiRobotuGib7.xlsx
+++ b/EXCELARSIV_PRODUCTS/kdv-iade-listesi-robotu-gib7/KdvIadeListesiRobotuGib7.xlsx
@@ -119,7 +119,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="87">
+  <fonts count="122">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -618,8 +618,214 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -811,8 +1017,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="35">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1175,11 +1405,353 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="323">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1706,6 +2278,235 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="18" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="18" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="18" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="18" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="90" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="92" fillId="18" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="90" fillId="18" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="18" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="65" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="98" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="65" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="102" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="104" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="105" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="106" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="17" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="109" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="17" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="12" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="11" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="116" fillId="18" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="121" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="107" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="118" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="118" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="12" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="11" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="107" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10723,7 +11524,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="173" t="inlineStr">
         <is>
@@ -10988,7 +11788,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="176" t="inlineStr">
         <is>
@@ -11122,7 +11921,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -11310,7 +12108,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -11333,9 +12130,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -12193,909 +12987,6 @@
         <v/>
       </c>
     </row>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993"/>
-    <row r="994"/>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
-    <row r="1000"/>
-    <row r="1001"/>
-    <row r="1002"/>
-    <row r="1003"/>
-    <row r="1004"/>
-    <row r="1005"/>
-    <row r="1006"/>
-    <row r="1007"/>
-    <row r="1008"/>
-    <row r="1009"/>
-    <row r="1010"/>
-    <row r="1011"/>
-    <row r="1012"/>
-    <row r="1013"/>
-    <row r="1014"/>
-    <row r="1015"/>
-    <row r="1016"/>
-    <row r="1017"/>
-    <row r="1018"/>
-    <row r="1019"/>
-    <row r="1020"/>
-    <row r="1021"/>
-    <row r="1022"/>
-    <row r="1023"/>
     <row r="1024" ht="20" customHeight="1">
       <c r="A1024" s="34" t="inlineStr">
         <is>
@@ -13226,7 +13117,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -13241,7 +13131,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -13549,8 +13438,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -13673,7 +13560,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -13688,7 +13574,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -15442,7 +15327,6 @@
         <v/>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="I60" s="22" t="inlineStr">
         <is>
@@ -15504,7 +15388,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -15519,7 +15402,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -15938,7 +15820,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -15953,7 +15834,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -16372,7 +16252,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -16387,7 +16266,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -16806,7 +16684,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -16821,7 +16698,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -17225,7 +17101,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -17240,7 +17115,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -17644,7 +17518,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -17659,7 +17532,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -18156,7 +18028,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -18171,7 +18042,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
@@ -18555,554 +18425,585 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="72.5" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
-    <col width="36.5" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="11.5" customWidth="1" min="7" max="7"/>
-    <col width="75.5" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15.5" customWidth="1" min="10" max="10"/>
-    <col width="81.5" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="79" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="226" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="95" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="227" t="inlineStr">
         <is>
           <t>KDV İADE LISTESI ROBOTU (GİB 7 LISTE)</t>
         </is>
       </c>
-      <c r="L2" s="96" t="inlineStr">
+      <c r="L2" s="228" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="97" t="inlineStr">
+      <c r="M2" s="229" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="98" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="230" t="inlineStr">
         <is>
           <t>Hedef Kullanıcı: SMMM, YMM, mali işler, ihracatçı · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="99" t="inlineStr">
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="231" t="inlineStr">
         <is>
           <t>İNDIRILECEK TOPLAM</t>
         </is>
       </c>
-      <c r="C5" s="100" t="n"/>
-      <c r="D5" s="101" t="inlineStr">
+      <c r="C5" s="232" t="n"/>
+      <c r="D5" s="233" t="inlineStr">
         <is>
           <t>KONSOLİDE</t>
         </is>
       </c>
-      <c r="E5" s="102" t="inlineStr">
+      <c r="E5" s="234" t="inlineStr">
         <is>
           <t>YÜKLENILEN TOPLAM</t>
         </is>
       </c>
-      <c r="F5" s="100" t="n"/>
-      <c r="G5" s="103" t="inlineStr">
+      <c r="F5" s="232" t="n"/>
+      <c r="G5" s="235" t="inlineStr">
         <is>
           <t>KONTROL</t>
         </is>
       </c>
-      <c r="H5" s="99" t="inlineStr">
+      <c r="H5" s="236" t="inlineStr">
         <is>
           <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
-      <c r="I5" s="100" t="n"/>
-      <c r="J5" s="104" t="inlineStr">
+      <c r="I5" s="232" t="n"/>
+      <c r="J5" s="237" t="inlineStr">
         <is>
           <t>GÜVENLİ</t>
         </is>
       </c>
-      <c r="K5" s="105" t="inlineStr">
+      <c r="K5" s="238" t="inlineStr">
         <is>
           <t>SİSTEM GÜVEN SKORU</t>
         </is>
       </c>
-      <c r="L5" s="100" t="n"/>
-      <c r="M5" s="101" t="inlineStr">
+      <c r="L5" s="232" t="n"/>
+      <c r="M5" s="239" t="inlineStr">
         <is>
           <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="106" t="n"/>
-      <c r="C6" s="100" t="n"/>
-      <c r="D6" s="100" t="n"/>
-      <c r="E6" s="107" t="n"/>
-      <c r="F6" s="100" t="n"/>
-      <c r="G6" s="100" t="n"/>
-      <c r="H6" s="106" t="n"/>
-      <c r="I6" s="100" t="n"/>
-      <c r="J6" s="100" t="n"/>
-      <c r="K6" s="108" t="n"/>
-      <c r="L6" s="100" t="n"/>
-      <c r="M6" s="100" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="196">
+    <row r="6" ht="6" customHeight="1">
+      <c r="B6" s="240" t="n"/>
+      <c r="C6" s="241" t="n"/>
+      <c r="D6" s="242" t="n"/>
+      <c r="E6" s="243" t="n"/>
+      <c r="F6" s="241" t="n"/>
+      <c r="G6" s="242" t="n"/>
+      <c r="H6" s="244" t="n"/>
+      <c r="I6" s="241" t="n"/>
+      <c r="J6" s="242" t="n"/>
+      <c r="K6" s="245" t="n"/>
+      <c r="L6" s="241" t="n"/>
+      <c r="M6" s="242" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="246">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="100" t="n"/>
-      <c r="D7" s="100" t="n"/>
-      <c r="E7" s="197">
+      <c r="C7" s="241" t="n"/>
+      <c r="D7" s="242" t="n"/>
+      <c r="E7" s="247">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="100" t="n"/>
-      <c r="G7" s="100" t="n"/>
-      <c r="H7" s="196">
+      <c r="F7" s="241" t="n"/>
+      <c r="G7" s="242" t="n"/>
+      <c r="H7" s="248">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="100" t="n"/>
-      <c r="J7" s="100" t="n"/>
-      <c r="K7" s="111">
+      <c r="I7" s="241" t="n"/>
+      <c r="J7" s="242" t="n"/>
+      <c r="K7" s="249">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="100" t="n"/>
-      <c r="M7" s="100" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="106" t="n"/>
-      <c r="C8" s="100" t="n"/>
-      <c r="D8" s="100" t="n"/>
-      <c r="E8" s="107" t="n"/>
-      <c r="F8" s="100" t="n"/>
-      <c r="G8" s="100" t="n"/>
-      <c r="H8" s="106" t="n"/>
-      <c r="I8" s="100" t="n"/>
-      <c r="J8" s="100" t="n"/>
-      <c r="K8" s="108" t="n"/>
-      <c r="L8" s="100" t="n"/>
-      <c r="M8" s="100" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="112" t="inlineStr">
+      <c r="L7" s="241" t="n"/>
+      <c r="M7" s="242" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="B8" s="240" t="n"/>
+      <c r="C8" s="241" t="n"/>
+      <c r="D8" s="242" t="n"/>
+      <c r="E8" s="243" t="n"/>
+      <c r="F8" s="241" t="n"/>
+      <c r="G8" s="242" t="n"/>
+      <c r="H8" s="244" t="n"/>
+      <c r="I8" s="241" t="n"/>
+      <c r="J8" s="242" t="n"/>
+      <c r="K8" s="245" t="n"/>
+      <c r="L8" s="241" t="n"/>
+      <c r="M8" s="242" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="250" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="100" t="n"/>
-      <c r="D9" s="100" t="n"/>
-      <c r="E9" s="113" t="inlineStr">
+      <c r="C9" s="251" t="n"/>
+      <c r="D9" s="252" t="n"/>
+      <c r="E9" s="253" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="100" t="n"/>
-      <c r="G9" s="100" t="n"/>
-      <c r="H9" s="112" t="inlineStr">
+      <c r="F9" s="251" t="n"/>
+      <c r="G9" s="252" t="n"/>
+      <c r="H9" s="254" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="100" t="n"/>
-      <c r="J9" s="100" t="n"/>
-      <c r="K9" s="114" t="inlineStr">
+      <c r="I9" s="251" t="n"/>
+      <c r="J9" s="252" t="n"/>
+      <c r="K9" s="255" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="100" t="n"/>
-      <c r="M9" s="100" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="93" t="inlineStr">
+      <c r="L9" s="251" t="n"/>
+      <c r="M9" s="252" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="256" t="inlineStr">
         <is>
           <t>KDV İADE LISTESI ROBOTU (GİB 7 LISTE) — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="115" t="inlineStr">
+      <c r="F11" s="257" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="93" t="inlineStr">
+      <c r="H11" s="256" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="92" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="98" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="92" t="inlineStr">
+      <c r="H12" s="98" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="116" t="inlineStr">
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="258" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="116" t="inlineStr">
+      <c r="C14" s="258" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="116" t="inlineStr">
+      <c r="D14" s="258" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="116" t="inlineStr">
+      <c r="E14" s="258" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="117" t="inlineStr">
+      <c r="H14" s="259" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="117" t="inlineStr">
+      <c r="I14" s="260" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="117" t="inlineStr">
+      <c r="J14" s="260" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="117" t="inlineStr">
+      <c r="K14" s="260" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="117" t="inlineStr">
+      <c r="L14" s="260" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="92" t="inlineStr">
+      <c r="M14" s="260" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="261" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="92" t="n">
+      <c r="C15" s="261" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="92" t="n">
+      <c r="D15" s="261" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="92" t="n">
+      <c r="E15" s="261" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="118" t="inlineStr">
+      <c r="H15" s="262" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="198">
+      <c r="I15" s="263">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="199">
+      <c r="J15" s="264">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="120" t="inlineStr">
+      <c r="K15" s="265" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="104" t="inlineStr">
+      <c r="L15" s="266" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="92" t="inlineStr">
+      <c r="M15" s="267" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="268" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="92" t="n">
+      <c r="C16" s="268" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="92" t="n">
+      <c r="D16" s="268" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="92" t="n">
+      <c r="E16" s="268" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="118" t="inlineStr">
+      <c r="H16" s="269" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="198">
+      <c r="I16" s="270">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="199">
+      <c r="J16" s="271">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="120" t="inlineStr">
+      <c r="K16" s="272" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="101" t="inlineStr">
+      <c r="L16" s="273" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="92" t="inlineStr">
+      <c r="M16" s="274" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="261" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="92" t="n">
+      <c r="C17" s="261" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="92" t="n">
+      <c r="D17" s="261" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="92" t="n">
+      <c r="E17" s="261" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="118" t="inlineStr">
+      <c r="H17" s="262" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="198">
+      <c r="I17" s="263">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="199">
+      <c r="J17" s="264">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="120" t="inlineStr">
+      <c r="K17" s="265" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="121" t="inlineStr">
+      <c r="L17" s="275" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="92" t="inlineStr">
+      <c r="M17" s="267" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="268" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="92" t="n">
+      <c r="C18" s="268" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="92" t="n">
+      <c r="D18" s="268" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="92" t="n">
+      <c r="E18" s="268" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="118" t="inlineStr">
+      <c r="H18" s="269" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="198">
+      <c r="I18" s="270">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="199">
+      <c r="J18" s="271">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="120" t="inlineStr">
+      <c r="K18" s="272" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="104" t="inlineStr">
+      <c r="L18" s="276" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="92" t="inlineStr">
+      <c r="M18" s="274" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="261" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="92" t="n">
+      <c r="C19" s="261" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="92" t="n">
+      <c r="D19" s="261" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="92" t="n">
+      <c r="E19" s="261" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="122" t="inlineStr">
+      <c r="H19" s="277" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="200">
+      <c r="I19" s="278">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="201">
+      <c r="J19" s="279">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="125" t="inlineStr"/>
-      <c r="L19" s="126" t="inlineStr">
+      <c r="K19" s="280" t="inlineStr"/>
+      <c r="L19" s="281" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="92" t="inlineStr">
+      <c r="M19" s="281" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="268" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="92" t="n">
+      <c r="C20" s="268" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="92" t="n">
+      <c r="D20" s="268" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="92" t="n">
+      <c r="E20" s="268" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="127" t="inlineStr">
+    <row r="21" ht="14" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="282" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="127" t="inlineStr">
+      <c r="C22" s="232" t="n"/>
+      <c r="D22" s="232" t="n"/>
+      <c r="E22" s="283" t="n"/>
+      <c r="F22" s="282" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="128" t="inlineStr">
+      <c r="G22" s="232" t="n"/>
+      <c r="H22" s="232" t="n"/>
+      <c r="I22" s="283" t="n"/>
+      <c r="K22" s="284" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="129" t="n"/>
-      <c r="M22" s="129" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="77" t="inlineStr">
+      <c r="L22" s="285" t="n"/>
+      <c r="M22" s="286" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="287" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="92" t="inlineStr">
+      <c r="C23" s="241" t="n"/>
+      <c r="D23" s="241" t="n"/>
+      <c r="E23" s="242" t="n"/>
+      <c r="F23" s="288" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="130" t="inlineStr">
+      <c r="G23" s="241" t="n"/>
+      <c r="H23" s="241" t="n"/>
+      <c r="I23" s="289" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="131" t="inlineStr">
-        <is>
-          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
-        </is>
-      </c>
-      <c r="L23" s="129" t="n"/>
-      <c r="M23" s="129" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="78" t="inlineStr">
+      <c r="K23" s="290" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="291" t="n"/>
+      <c r="M23" s="292" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="293" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="92" t="inlineStr">
+      <c r="C24" s="241" t="n"/>
+      <c r="D24" s="241" t="n"/>
+      <c r="E24" s="242" t="n"/>
+      <c r="F24" s="288" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="130" t="inlineStr">
+      <c r="G24" s="241" t="n"/>
+      <c r="H24" s="241" t="n"/>
+      <c r="I24" s="289" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="132" t="inlineStr">
-        <is>
-          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="133" t="inlineStr">
+      <c r="K24" s="294" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="295" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="77" t="inlineStr">
+      <c r="C25" s="241" t="n"/>
+      <c r="D25" s="241" t="n"/>
+      <c r="E25" s="242" t="n"/>
+      <c r="F25" s="266" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="134" t="inlineStr">
+      <c r="G25" s="296" t="n"/>
+      <c r="H25" s="296" t="n"/>
+      <c r="I25" s="296" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="297" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="135" t="inlineStr">
+      <c r="C26" s="241" t="n"/>
+      <c r="D26" s="241" t="n"/>
+      <c r="E26" s="242" t="n"/>
+      <c r="F26" s="298" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
@@ -19110,23 +19011,29 @@
       <c r="G26" s="208" t="n"/>
       <c r="H26" s="208" t="n"/>
       <c r="I26" s="209" t="n"/>
-      <c r="K26" s="136" t="inlineStr">
-        <is>
-          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="K26" s="299" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="300" t="n"/>
+      <c r="C27" s="251" t="n"/>
+      <c r="D27" s="251" t="n"/>
+      <c r="E27" s="252" t="n"/>
       <c r="F27" s="210" t="n"/>
       <c r="G27" s="211" t="n"/>
       <c r="H27" s="211" t="n"/>
       <c r="I27" s="212" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19161,7 +19068,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -19169,7 +19075,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="46" t="inlineStr">
         <is>
@@ -19285,7 +19190,6 @@
         <v>1050000</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
@@ -19308,7 +19212,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
@@ -19414,7 +19317,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -19437,7 +19339,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
@@ -19607,7 +19508,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -19615,7 +19515,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
@@ -19840,8 +19739,6 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -19920,7 +19817,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -19961,7 +19857,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
@@ -20046,7 +19941,6 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
@@ -20109,7 +20003,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -20121,7 +20014,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
@@ -20144,7 +20036,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
@@ -20156,7 +20047,6 @@
         <v/>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
@@ -20173,7 +20063,6 @@
       </c>
       <c r="B32" s="25" t="inlineStr"/>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="61" t="inlineStr">
         <is>
@@ -20252,7 +20141,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -20260,7 +20148,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
@@ -20404,7 +20291,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
@@ -20495,7 +20381,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -21058,7 +20943,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -21066,7 +20950,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="46" t="inlineStr">
         <is>
@@ -21119,7 +21002,6 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
@@ -21250,7 +21132,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="225" t="inlineStr">
         <is>
@@ -21258,7 +21139,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
@@ -22319,7 +22199,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="B33" s="66" t="inlineStr">
         <is>
@@ -22327,7 +22206,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="B35" s="61" t="inlineStr">
         <is>
@@ -22386,7 +22264,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
         <is>
@@ -22394,7 +22271,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="43" t="inlineStr">
         <is>
@@ -22423,7 +22299,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
@@ -22480,7 +22355,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="67" t="inlineStr">
         <is>
@@ -22495,7 +22369,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -22520,7 +22393,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
@@ -22535,7 +22407,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="69" t="inlineStr">
         <is>
@@ -22597,7 +22468,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="137" t="inlineStr">
         <is>
@@ -22618,7 +22488,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="140" t="inlineStr">
         <is>
@@ -23031,7 +22900,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="157" t="inlineStr">
         <is>
@@ -23062,54 +22930,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="79" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="226" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="B2" s="159" t="inlineStr">
         <is>
           <t>KDV İADE LISTESI ROBOTU (GİB 7 LISTE) — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="160" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="301" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · SMMM, YMM, mali işler, ihracatçı</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="161" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="302" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="162" t="inlineStr">
+    <row r="5" ht="12" customHeight="1"/>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="303" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
@@ -23118,7 +22987,7 @@
       <c r="D6" s="213" t="n"/>
       <c r="E6" s="213" t="n"/>
       <c r="F6" s="214" t="n"/>
-      <c r="H6" s="163" t="inlineStr">
+      <c r="H6" s="304" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
@@ -23128,151 +22997,151 @@
       <c r="K6" s="213" t="n"/>
       <c r="L6" s="214" t="n"/>
     </row>
-    <row r="7">
-      <c r="B7" s="100" t="n"/>
-      <c r="C7" s="100" t="n"/>
-      <c r="D7" s="100" t="n"/>
-      <c r="E7" s="100" t="n"/>
-      <c r="F7" s="100" t="n"/>
-      <c r="H7" s="100" t="n"/>
-      <c r="I7" s="100" t="n"/>
-      <c r="J7" s="100" t="n"/>
-      <c r="K7" s="100" t="n"/>
-      <c r="L7" s="100" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="164" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="305" t="n"/>
+      <c r="C7" s="241" t="n"/>
+      <c r="D7" s="241" t="n"/>
+      <c r="E7" s="241" t="n"/>
+      <c r="F7" s="306" t="n"/>
+      <c r="H7" s="307" t="n"/>
+      <c r="I7" s="241" t="n"/>
+      <c r="J7" s="241" t="n"/>
+      <c r="K7" s="241" t="n"/>
+      <c r="L7" s="308" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="309" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="100" t="n"/>
-      <c r="D8" s="100" t="n"/>
-      <c r="E8" s="165" t="inlineStr">
+      <c r="C8" s="241" t="n"/>
+      <c r="D8" s="241" t="n"/>
+      <c r="E8" s="310" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="100" t="n"/>
-      <c r="H8" s="164" t="inlineStr">
+      <c r="F8" s="306" t="n"/>
+      <c r="H8" s="311" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="100" t="n"/>
-      <c r="J8" s="100" t="n"/>
-      <c r="K8" s="166" t="inlineStr">
+      <c r="I8" s="241" t="n"/>
+      <c r="J8" s="241" t="n"/>
+      <c r="K8" s="312" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="100" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="164" t="inlineStr">
+      <c r="L8" s="308" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="309" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="100" t="n"/>
-      <c r="D9" s="100" t="n"/>
-      <c r="E9" s="203">
+      <c r="C9" s="241" t="n"/>
+      <c r="D9" s="241" t="n"/>
+      <c r="E9" s="313">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="100" t="n"/>
-      <c r="H9" s="164" t="inlineStr">
+      <c r="F9" s="306" t="n"/>
+      <c r="H9" s="311" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="100" t="n"/>
-      <c r="J9" s="100" t="n"/>
-      <c r="K9" s="203">
+      <c r="I9" s="241" t="n"/>
+      <c r="J9" s="241" t="n"/>
+      <c r="K9" s="313">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="100" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="164" t="inlineStr">
+      <c r="L9" s="308" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="309" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="100" t="n"/>
-      <c r="D10" s="100" t="n"/>
-      <c r="E10" s="204">
+      <c r="C10" s="241" t="n"/>
+      <c r="D10" s="241" t="n"/>
+      <c r="E10" s="314">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="100" t="n"/>
-      <c r="H10" s="164" t="inlineStr">
+      <c r="F10" s="306" t="n"/>
+      <c r="H10" s="311" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="100" t="n"/>
-      <c r="J10" s="100" t="n"/>
-      <c r="K10" s="204">
+      <c r="I10" s="241" t="n"/>
+      <c r="J10" s="241" t="n"/>
+      <c r="K10" s="314">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="100" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="164" t="inlineStr">
+      <c r="L10" s="308" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="309" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="100" t="n"/>
-      <c r="D11" s="100" t="n"/>
-      <c r="E11" s="205">
+      <c r="C11" s="241" t="n"/>
+      <c r="D11" s="241" t="n"/>
+      <c r="E11" s="315">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="100" t="n"/>
-      <c r="H11" s="164" t="inlineStr">
+      <c r="F11" s="306" t="n"/>
+      <c r="H11" s="311" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="100" t="n"/>
-      <c r="J11" s="100" t="n"/>
-      <c r="K11" s="168" t="inlineStr">
+      <c r="I11" s="241" t="n"/>
+      <c r="J11" s="241" t="n"/>
+      <c r="K11" s="316" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="100" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="100" t="n"/>
-      <c r="C12" s="100" t="n"/>
-      <c r="D12" s="100" t="n"/>
-      <c r="E12" s="100" t="n"/>
-      <c r="F12" s="100" t="n"/>
-      <c r="H12" s="100" t="n"/>
-      <c r="I12" s="100" t="n"/>
-      <c r="J12" s="100" t="n"/>
-      <c r="K12" s="100" t="n"/>
-      <c r="L12" s="100" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="100" t="n"/>
-      <c r="C13" s="100" t="n"/>
-      <c r="D13" s="100" t="n"/>
-      <c r="E13" s="100" t="n"/>
-      <c r="F13" s="100" t="n"/>
-      <c r="H13" s="100" t="n"/>
-      <c r="I13" s="100" t="n"/>
-      <c r="J13" s="100" t="n"/>
-      <c r="K13" s="100" t="n"/>
-      <c r="L13" s="100" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="169" t="inlineStr">
+      <c r="L11" s="308" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="305" t="n"/>
+      <c r="C12" s="241" t="n"/>
+      <c r="D12" s="241" t="n"/>
+      <c r="E12" s="241" t="n"/>
+      <c r="F12" s="306" t="n"/>
+      <c r="H12" s="307" t="n"/>
+      <c r="I12" s="241" t="n"/>
+      <c r="J12" s="241" t="n"/>
+      <c r="K12" s="241" t="n"/>
+      <c r="L12" s="308" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="305" t="n"/>
+      <c r="C13" s="241" t="n"/>
+      <c r="D13" s="241" t="n"/>
+      <c r="E13" s="241" t="n"/>
+      <c r="F13" s="306" t="n"/>
+      <c r="H13" s="307" t="n"/>
+      <c r="I13" s="241" t="n"/>
+      <c r="J13" s="241" t="n"/>
+      <c r="K13" s="241" t="n"/>
+      <c r="L13" s="308" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="317" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
@@ -23281,7 +23150,7 @@
       <c r="D14" s="215" t="n"/>
       <c r="E14" s="215" t="n"/>
       <c r="F14" s="216" t="n"/>
-      <c r="H14" s="170" t="inlineStr">
+      <c r="H14" s="318" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
@@ -23291,7 +23160,7 @@
       <c r="K14" s="217" t="n"/>
       <c r="L14" s="218" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="219" t="n"/>
       <c r="C15" s="220" t="n"/>
       <c r="D15" s="220" t="n"/>
@@ -23303,70 +23172,185 @@
       <c r="K15" s="223" t="n"/>
       <c r="L15" s="224" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="80" t="inlineStr">
+    <row r="16" ht="10" customHeight="1"/>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="319" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="127" t="inlineStr">
+      <c r="C17" s="232" t="n"/>
+      <c r="D17" s="232" t="n"/>
+      <c r="E17" s="232" t="n"/>
+      <c r="F17" s="232" t="n"/>
+      <c r="G17" s="232" t="n"/>
+      <c r="H17" s="232" t="n"/>
+      <c r="I17" s="232" t="n"/>
+      <c r="J17" s="232" t="n"/>
+      <c r="K17" s="232" t="n"/>
+      <c r="L17" s="283" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="320" t="n"/>
+      <c r="C18" s="241" t="n"/>
+      <c r="D18" s="241" t="n"/>
+      <c r="E18" s="241" t="n"/>
+      <c r="F18" s="241" t="n"/>
+      <c r="G18" s="241" t="n"/>
+      <c r="H18" s="241" t="n"/>
+      <c r="I18" s="241" t="n"/>
+      <c r="J18" s="241" t="n"/>
+      <c r="K18" s="241" t="n"/>
+      <c r="L18" s="242" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="321" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="171" t="inlineStr">
+      <c r="C19" s="241" t="n"/>
+      <c r="D19" s="241" t="n"/>
+      <c r="E19" s="241" t="n"/>
+      <c r="F19" s="241" t="n"/>
+      <c r="G19" s="241" t="n"/>
+      <c r="H19" s="241" t="n"/>
+      <c r="I19" s="241" t="n"/>
+      <c r="J19" s="241" t="n"/>
+      <c r="K19" s="241" t="n"/>
+      <c r="L19" s="242" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="322" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="127" t="inlineStr">
+      <c r="C20" s="241" t="n"/>
+      <c r="D20" s="241" t="n"/>
+      <c r="E20" s="241" t="n"/>
+      <c r="F20" s="241" t="n"/>
+      <c r="G20" s="241" t="n"/>
+      <c r="H20" s="241" t="n"/>
+      <c r="I20" s="241" t="n"/>
+      <c r="J20" s="241" t="n"/>
+      <c r="K20" s="241" t="n"/>
+      <c r="L20" s="242" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="321" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="171" t="inlineStr">
+      <c r="C21" s="241" t="n"/>
+      <c r="D21" s="241" t="n"/>
+      <c r="E21" s="241" t="n"/>
+      <c r="F21" s="241" t="n"/>
+      <c r="G21" s="241" t="n"/>
+      <c r="H21" s="241" t="n"/>
+      <c r="I21" s="241" t="n"/>
+      <c r="J21" s="241" t="n"/>
+      <c r="K21" s="241" t="n"/>
+      <c r="L21" s="242" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="322" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="127" t="inlineStr">
+      <c r="C22" s="241" t="n"/>
+      <c r="D22" s="241" t="n"/>
+      <c r="E22" s="241" t="n"/>
+      <c r="F22" s="241" t="n"/>
+      <c r="G22" s="241" t="n"/>
+      <c r="H22" s="241" t="n"/>
+      <c r="I22" s="241" t="n"/>
+      <c r="J22" s="241" t="n"/>
+      <c r="K22" s="241" t="n"/>
+      <c r="L22" s="242" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="321" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="171" t="inlineStr">
+      <c r="C23" s="241" t="n"/>
+      <c r="D23" s="241" t="n"/>
+      <c r="E23" s="241" t="n"/>
+      <c r="F23" s="241" t="n"/>
+      <c r="G23" s="241" t="n"/>
+      <c r="H23" s="241" t="n"/>
+      <c r="I23" s="241" t="n"/>
+      <c r="J23" s="241" t="n"/>
+      <c r="K23" s="241" t="n"/>
+      <c r="L23" s="242" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="322" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="127" t="inlineStr">
+      <c r="C24" s="241" t="n"/>
+      <c r="D24" s="241" t="n"/>
+      <c r="E24" s="241" t="n"/>
+      <c r="F24" s="241" t="n"/>
+      <c r="G24" s="241" t="n"/>
+      <c r="H24" s="241" t="n"/>
+      <c r="I24" s="241" t="n"/>
+      <c r="J24" s="241" t="n"/>
+      <c r="K24" s="241" t="n"/>
+      <c r="L24" s="242" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="321" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="171" t="inlineStr">
+      <c r="C25" s="241" t="n"/>
+      <c r="D25" s="241" t="n"/>
+      <c r="E25" s="241" t="n"/>
+      <c r="F25" s="241" t="n"/>
+      <c r="G25" s="241" t="n"/>
+      <c r="H25" s="241" t="n"/>
+      <c r="I25" s="241" t="n"/>
+      <c r="J25" s="241" t="n"/>
+      <c r="K25" s="241" t="n"/>
+      <c r="L25" s="242" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="322" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="241" t="n"/>
+      <c r="D26" s="241" t="n"/>
+      <c r="E26" s="241" t="n"/>
+      <c r="F26" s="241" t="n"/>
+      <c r="G26" s="241" t="n"/>
+      <c r="H26" s="241" t="n"/>
+      <c r="I26" s="241" t="n"/>
+      <c r="J26" s="241" t="n"/>
+      <c r="K26" s="241" t="n"/>
+      <c r="L26" s="242" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="300" t="n"/>
+      <c r="C27" s="251" t="n"/>
+      <c r="D27" s="251" t="n"/>
+      <c r="E27" s="251" t="n"/>
+      <c r="F27" s="251" t="n"/>
+      <c r="G27" s="251" t="n"/>
+      <c r="H27" s="251" t="n"/>
+      <c r="I27" s="251" t="n"/>
+      <c r="J27" s="251" t="n"/>
+      <c r="K27" s="251" t="n"/>
+      <c r="L27" s="252" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -23408,7 +23392,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="178" t="inlineStr">
         <is>
@@ -23903,7 +23886,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="181" t="inlineStr">
         <is>
@@ -24650,7 +24632,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="186" t="inlineStr">
         <is>
@@ -25328,7 +25309,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="190" t="inlineStr">
         <is>
@@ -25878,7 +25858,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="193" t="inlineStr">
         <is>
